--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Río Breogán.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Río Breogán.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2149.84</v>
+        <v>2476.559999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2155.1</v>
+        <v>2481.8</v>
       </c>
       <c r="D2" t="n">
-        <v>117.0711335900886</v>
+        <v>117.5356596019018</v>
       </c>
       <c r="E2" t="n">
-        <v>120.7832583174795</v>
+        <v>119.8726730598759</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5537345513164965</v>
+        <v>0.5593061415846226</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1530873277267931</v>
+        <v>0.1527430986622773</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3541247484909457</v>
+        <v>0.3460176991150443</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2482536270822139</v>
+        <v>0.2489451476793249</v>
       </c>
       <c r="J2" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="L2" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="M2" t="n">
-        <v>358</v>
+        <v>412</v>
       </c>
       <c r="N2" t="n">
-        <v>835</v>
+        <v>954</v>
       </c>
       <c r="O2" t="n">
-        <v>1110</v>
+        <v>1258</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5964535196131112</v>
+        <v>0.5897796530707923</v>
       </c>
       <c r="Q2" t="n">
+        <v>154</v>
+      </c>
+      <c r="R2" t="n">
+        <v>353</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1654946085325832</v>
+      </c>
+      <c r="T2" t="n">
+        <v>112</v>
+      </c>
+      <c r="U2" t="n">
+        <v>283</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1326769807782466</v>
+      </c>
+      <c r="W2" t="n">
         <v>125</v>
       </c>
-      <c r="R2" t="n">
-        <v>294</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1579795808704997</v>
-      </c>
-      <c r="T2" t="n">
-        <v>93</v>
-      </c>
-      <c r="U2" t="n">
-        <v>241</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.1295002686727566</v>
-      </c>
-      <c r="W2" t="n">
-        <v>111</v>
-      </c>
       <c r="X2" t="n">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1321869962385814</v>
+        <v>0.1303328645100797</v>
       </c>
       <c r="Z2" t="n">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="AA2" t="n">
-        <v>556</v>
+        <v>635</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2987641053197206</v>
+        <v>0.2977027660571964</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7522522522522522</v>
+        <v>0.7583465818759937</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4251700680272109</v>
+        <v>0.4362606232294617</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3858921161825726</v>
+        <v>0.3957597173144876</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.451219512195122</v>
+        <v>0.4496402877697842</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3273381294964029</v>
+        <v>0.3322834645669291</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.504504504504504</v>
+        <v>1.516693163751987</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7717842323651453</v>
+        <v>0.7915194346289752</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.096009975062344</v>
+        <v>1.104052573932092</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.9052369077306733</v>
+        <v>0.8922413793103449</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9971590909090909</v>
+        <v>0.979539641943734</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.786666666666667</v>
+        <v>1.747126436781609</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.287206266318538</v>
+        <v>1.331050228310502</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.859007832898173</v>
+        <v>4.86986301369863</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.14621409921671</v>
+        <v>6.200913242009133</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.77999999999999</v>
+        <v>77.39249999999998</v>
       </c>
       <c r="C3" t="n">
-        <v>76.96785714285714</v>
+        <v>77.55625000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>117.0711335900886</v>
+        <v>117.5356596019018</v>
       </c>
       <c r="E3" t="n">
-        <v>120.7832583174795</v>
+        <v>119.8726730598759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5537345513164966</v>
+        <v>0.5593061415846226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1530873277267931</v>
+        <v>0.1527430986622773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3541247484909457</v>
+        <v>0.3460176991150443</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2482536270822139</v>
+        <v>0.2489451476793249</v>
       </c>
       <c r="J3" t="n">
-        <v>12.96428571428571</v>
+        <v>12.9375</v>
       </c>
       <c r="K3" t="n">
-        <v>12.53571428571429</v>
+        <v>11.96875</v>
       </c>
       <c r="L3" t="n">
-        <v>4.785714285714286</v>
+        <v>4.75</v>
       </c>
       <c r="M3" t="n">
-        <v>12.78571428571429</v>
+        <v>12.875</v>
       </c>
       <c r="N3" t="n">
-        <v>29.82142857142857</v>
+        <v>29.8125</v>
       </c>
       <c r="O3" t="n">
-        <v>39.64285714285715</v>
+        <v>39.3125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5964535196131113</v>
+        <v>0.5897796530707923</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.464285714285714</v>
+        <v>4.8125</v>
       </c>
       <c r="R3" t="n">
-        <v>10.5</v>
+        <v>11.03125</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1579795808704997</v>
+        <v>0.1654946085325832</v>
       </c>
       <c r="T3" t="n">
-        <v>3.321428571428572</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>8.607142857142858</v>
+        <v>8.84375</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1295002686727566</v>
+        <v>0.1326769807782466</v>
       </c>
       <c r="W3" t="n">
-        <v>3.964285714285714</v>
+        <v>3.90625</v>
       </c>
       <c r="X3" t="n">
-        <v>8.785714285714286</v>
+        <v>8.6875</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1321869962385814</v>
+        <v>0.1303328645100797</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>6.59375</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.85714285714286</v>
+        <v>19.84375</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2987641053197206</v>
+        <v>0.2977027660571964</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7522522522522522</v>
+        <v>0.7583465818759937</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4251700680272109</v>
+        <v>0.4362606232294617</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3858921161825726</v>
+        <v>0.3957597173144876</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4512195121951219</v>
+        <v>0.4496402877697842</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3273381294964029</v>
+        <v>0.3322834645669291</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.504504504504504</v>
+        <v>1.516693163751987</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7717842323651453</v>
+        <v>0.7915194346289752</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.096009975062344</v>
+        <v>1.104052573932092</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.9052369077306733</v>
+        <v>0.8922413793103449</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9971590909090909</v>
+        <v>0.979539641943734</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.786666666666667</v>
+        <v>1.747126436781609</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.287206266318538</v>
+        <v>1.331050228310502</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.859007832898172</v>
+        <v>4.86986301369863</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.14621409921671</v>
+        <v>6.200913242009133</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2160.36</v>
+        <v>2487.04</v>
       </c>
       <c r="C4" t="n">
-        <v>2155.1</v>
+        <v>2481.8</v>
       </c>
       <c r="D4" t="n">
-        <v>120.7832583174795</v>
+        <v>119.8726730598759</v>
       </c>
       <c r="E4" t="n">
-        <v>117.0711335900886</v>
+        <v>117.5356596019018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5851358846367166</v>
+        <v>0.5825289575289575</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1605052914712051</v>
+        <v>0.1615014061760365</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3546694648478489</v>
+        <v>0.3499546690843155</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2734331669439822</v>
+        <v>0.2707528957528957</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="K4" t="n">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="L4" t="n">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="M4" t="n">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="N4" t="n">
-        <v>896</v>
+        <v>1036</v>
       </c>
       <c r="O4" t="n">
-        <v>1222</v>
+        <v>1409</v>
       </c>
       <c r="P4" t="n">
-        <v>0.677759290072102</v>
+        <v>0.680019305019305</v>
       </c>
       <c r="Q4" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="R4" t="n">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1381031613976705</v>
+        <v>0.138996138996139</v>
       </c>
       <c r="T4" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1125901275651692</v>
+        <v>0.1090733590733591</v>
       </c>
       <c r="W4" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="X4" t="n">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1314475873544093</v>
+        <v>0.1312741312741313</v>
       </c>
       <c r="Z4" t="n">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="AA4" t="n">
-        <v>561</v>
+        <v>643</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3111480865224626</v>
+        <v>0.3103281853281853</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7332242225859247</v>
+        <v>0.7352732434350603</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.429718875502008</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3645320197044335</v>
+        <v>0.3451327433628318</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4135021097046414</v>
+        <v>0.4044117647058824</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3850267379679144</v>
+        <v>0.3794712286158631</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.466448445171849</v>
+        <v>1.470546486870121</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.729064039408867</v>
+        <v>0.6902654867256637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.180451127819549</v>
+        <v>1.160655737704918</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8929503916449086</v>
+        <v>0.8835616438356164</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.050295857988166</v>
+        <v>1.018134715025907</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.634615384615385</v>
+        <v>1.637096774193548</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.336658354114713</v>
+        <v>1.355603448275862</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.496259351620948</v>
+        <v>4.46551724137931</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.832917705735661</v>
+        <v>5.821120689655173</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.15571428571427</v>
+        <v>77.71999999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>76.96785714285714</v>
+        <v>77.55625000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>120.7832583174795</v>
+        <v>119.8726730598759</v>
       </c>
       <c r="E5" t="n">
-        <v>117.0711335900886</v>
+        <v>117.5356596019018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5851358846367166</v>
+        <v>0.5825289575289575</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1605052914712051</v>
+        <v>0.1615014061760365</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3546694648478489</v>
+        <v>0.3499546690843155</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2734331669439823</v>
+        <v>0.2707528957528957</v>
       </c>
       <c r="J5" t="n">
-        <v>12.21428571428571</v>
+        <v>12.09375</v>
       </c>
       <c r="K5" t="n">
-        <v>12.67857142857143</v>
+        <v>12.28125</v>
       </c>
       <c r="L5" t="n">
-        <v>6.071428571428571</v>
+        <v>6.34375</v>
       </c>
       <c r="M5" t="n">
-        <v>13.42857142857143</v>
+        <v>13.65625</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>32.375</v>
       </c>
       <c r="O5" t="n">
-        <v>43.64285714285715</v>
+        <v>44.03125</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6777592900721021</v>
+        <v>0.680019305019305</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.821428571428572</v>
+        <v>3.84375</v>
       </c>
       <c r="R5" t="n">
-        <v>8.892857142857142</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1381031613976705</v>
+        <v>0.138996138996139</v>
       </c>
       <c r="T5" t="n">
-        <v>2.642857142857143</v>
+        <v>2.4375</v>
       </c>
       <c r="U5" t="n">
-        <v>7.25</v>
+        <v>7.0625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1125901275651692</v>
+        <v>0.1090733590733591</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5</v>
+        <v>3.4375</v>
       </c>
       <c r="X5" t="n">
-        <v>8.464285714285714</v>
+        <v>8.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1314475873544093</v>
+        <v>0.1312741312741313</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.714285714285714</v>
+        <v>7.625</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.03571428571428</v>
+        <v>20.09375</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3111480865224626</v>
+        <v>0.3103281853281853</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7332242225859247</v>
+        <v>0.7352732434350603</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4297188755020081</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3645320197044335</v>
+        <v>0.3451327433628318</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4135021097046414</v>
+        <v>0.4044117647058824</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3850267379679145</v>
+        <v>0.3794712286158631</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.466448445171849</v>
+        <v>1.470546486870121</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.729064039408867</v>
+        <v>0.6902654867256637</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.180451127819549</v>
+        <v>1.160655737704918</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8929503916449085</v>
+        <v>0.8835616438356164</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.050295857988166</v>
+        <v>1.018134715025907</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.634615384615385</v>
+        <v>1.637096774193548</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.336658354114713</v>
+        <v>1.355603448275862</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.496259351620948</v>
+        <v>4.46551724137931</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.83291770573566</v>
+        <v>5.821120689655173</v>
       </c>
     </row>
     <row r="7">
@@ -1419,67 +1419,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F8" t="n">
         <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H8" t="n">
+        <v>43</v>
+      </c>
+      <c r="I8" t="n">
+        <v>56</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" t="n">
+        <v>54</v>
+      </c>
+      <c r="L8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M8" t="n">
+        <v>31</v>
+      </c>
+      <c r="N8" t="n">
+        <v>29</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="n">
+        <v>71</v>
+      </c>
+      <c r="S8" t="n">
+        <v>44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>246</v>
+      </c>
+      <c r="U8" t="n">
         <v>35</v>
       </c>
-      <c r="I8" t="n">
+      <c r="V8" t="n">
         <v>47</v>
-      </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" t="n">
-        <v>46</v>
-      </c>
-      <c r="L8" t="n">
-        <v>42</v>
-      </c>
-      <c r="M8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N8" t="n">
-        <v>26</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R8" t="n">
-        <v>65</v>
-      </c>
-      <c r="S8" t="n">
-        <v>35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>203</v>
-      </c>
-      <c r="U8" t="n">
-        <v>26</v>
-      </c>
-      <c r="V8" t="n">
-        <v>40</v>
       </c>
       <c r="W8" t="n">
         <v>23</v>
@@ -1488,28 +1488,28 @@
         <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="Z8" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.706</v>
+        <v>0.731</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.444</v>
+        <v>0.435</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1518,57 +1518,57 @@
         <v>12</v>
       </c>
       <c r="AI8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.353</v>
+        <v>0.343</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.217</v>
+        <v>0.192</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>440:59</t>
+          <t>501:36</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>166.68</v>
+        <v>192.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.526</v>
+        <v>0.52</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.569</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.056</v>
+        <v>1.049</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.261</v>
+        <v>0.281</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.167</v>
+        <v>1.133</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.169</v>
+        <v>0.171</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.107</v>
+        <v>0.113</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.123</v>
+        <v>0.125</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="9">
@@ -1578,156 +1578,156 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" t="n">
+        <v>104</v>
+      </c>
+      <c r="F9" t="n">
         <v>46</v>
       </c>
-      <c r="E9" t="n">
-        <v>91</v>
-      </c>
-      <c r="F9" t="n">
-        <v>39</v>
-      </c>
       <c r="G9" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H9" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I9" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K9" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q9" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R9" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="S9" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="T9" t="n">
-        <v>309</v>
+        <v>361</v>
       </c>
       <c r="U9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="V9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="Z9" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.864</v>
+        <v>0.869</v>
       </c>
       <c r="AB9" t="n">
         <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.308</v>
+        <v>0.375</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.417</v>
+        <v>0.447</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.358</v>
+        <v>0.382</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>543:41</t>
+          <t>623:12</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>266.84</v>
+        <v>302.36</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.539</v>
+        <v>0.569</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.625</v>
+        <v>0.648</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.087</v>
+        <v>1.111</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.131</v>
+        <v>0.142</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.418</v>
+        <v>0.404</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.857</v>
+        <v>0.767</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.22</v>
+        <v>0.217</v>
       </c>
       <c r="AW9" t="n">
         <v>0.029</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="10">
@@ -1737,22 +1737,22 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1773,64 +1773,64 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1842,42 +1842,42 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.5</v>
+        <v>0.308</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.287</v>
+        <v>0.294</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -1896,40 +1896,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E11" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H11" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J11" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N11" t="n">
         <v>12</v>
@@ -1938,58 +1938,58 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="R11" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="S11" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="T11" t="n">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="U11" t="n">
         <v>39</v>
       </c>
       <c r="V11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Z11" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AC11" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.327</v>
+        <v>0.344</v>
       </c>
       <c r="AE11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF11" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.426</v>
+        <v>0.441</v>
       </c>
       <c r="AH11" t="n">
         <v>2</v>
@@ -2001,51 +2001,51 @@
         <v>0.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.317</v>
+        <v>0.313</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>550:26</t>
+          <t>605:21</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>310.36</v>
+        <v>339.24</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.453</v>
+        <v>0.457</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.483</v>
+        <v>0.487</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.786</v>
+        <v>0.79</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.187</v>
+        <v>0.189</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.142</v>
+        <v>0.137</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.259</v>
+        <v>2.359</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.252</v>
+        <v>0.25</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.166</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="12">
@@ -2055,16 +2055,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2073,82 +2073,82 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I12" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>20</v>
+      </c>
+      <c r="R12" t="n">
+        <v>63</v>
+      </c>
+      <c r="S12" t="n">
+        <v>47</v>
+      </c>
+      <c r="T12" t="n">
+        <v>135</v>
+      </c>
+      <c r="U12" t="n">
+        <v>17</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>106</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>16</v>
-      </c>
-      <c r="R12" t="n">
-        <v>54</v>
-      </c>
-      <c r="S12" t="n">
-        <v>31</v>
-      </c>
-      <c r="T12" t="n">
-        <v>72</v>
-      </c>
-      <c r="U12" t="n">
-        <v>12</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AF12" t="n">
         <v>7</v>
       </c>
-      <c r="AC12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>4</v>
-      </c>
       <c r="AG12" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2170,41 +2170,41 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>242:11</t>
+          <t>319:39</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>87.64</v>
+        <v>130.44</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.603</v>
+        <v>0.614</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.6</v>
+        <v>0.616</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.981</v>
+        <v>1.043</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.183</v>
+        <v>0.153</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.276</v>
+        <v>0.318</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.162</v>
+        <v>0.182</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="13">
@@ -2214,153 +2214,153 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E13" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="H13" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I13" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J13" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K13" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="R13" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="S13" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="T13" t="n">
-        <v>407</v>
+        <v>456</v>
       </c>
       <c r="U13" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V13" t="n">
         <v>25</v>
       </c>
       <c r="W13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="Z13" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AA13" t="n">
         <v>0.826</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AC13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF13" t="n">
         <v>32</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>28</v>
-      </c>
       <c r="AG13" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.375</v>
+        <v>0.395</v>
       </c>
       <c r="AK13" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AL13" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.422</v>
+        <v>0.405</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>610:42</t>
+          <t>702:40</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>346.08</v>
+        <v>393.16</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.571</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.656</v>
+        <v>0.646</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.156</v>
+        <v>1.137</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.118</v>
+        <v>0.12</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.478</v>
+        <v>0.439</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.951</v>
+        <v>0.979</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.254</v>
+        <v>0.25</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="AY13" t="n">
         <v>0.051</v>
@@ -2373,40 +2373,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I14" t="n">
+        <v>37</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29</v>
+      </c>
+      <c r="K14" t="n">
+        <v>111</v>
+      </c>
+      <c r="L14" t="n">
+        <v>35</v>
+      </c>
+      <c r="M14" t="n">
         <v>26</v>
-      </c>
-      <c r="J14" t="n">
-        <v>19</v>
-      </c>
-      <c r="K14" t="n">
-        <v>94</v>
-      </c>
-      <c r="L14" t="n">
-        <v>33</v>
-      </c>
-      <c r="M14" t="n">
-        <v>25</v>
       </c>
       <c r="N14" t="n">
         <v>7</v>
@@ -2415,25 +2415,25 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R14" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>220</v>
+        <v>276</v>
       </c>
       <c r="U14" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="W14" t="n">
         <v>17</v>
@@ -2442,87 +2442,87 @@
         <v>8</v>
       </c>
       <c r="Y14" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.792</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.333</v>
+        <v>0.389</v>
       </c>
       <c r="AE14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF14" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.395</v>
+        <v>0.415</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.526</v>
+        <v>0.511</v>
       </c>
       <c r="AK14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.22</v>
+        <v>0.255</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>592:55</t>
+          <t>673:53</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>188.44</v>
+        <v>217.28</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.506</v>
+        <v>0.532</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.536</v>
+        <v>0.569</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.992</v>
+        <v>1.054</v>
       </c>
       <c r="AS14" t="n">
         <v>0.074</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.135</v>
+        <v>0.173</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.357</v>
+        <v>1.812</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.142</v>
+        <v>0.144</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.186</v>
+        <v>0.191</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.023</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="15">
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E15" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2550,19 +2550,19 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J15" t="n">
         <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L15" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M15" t="n">
         <v>13</v>
@@ -2580,19 +2580,19 @@
         <v>28</v>
       </c>
       <c r="R15" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="S15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T15" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="U15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="W15" t="n">
         <v>2</v>
@@ -2601,22 +2601,22 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.748</v>
+        <v>0.743</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.48</v>
+        <v>0.519</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2647,41 +2647,41 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>425:05</t>
+          <t>436:39</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>136.8</v>
+        <v>139.68</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.674</v>
+        <v>0.681</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.096</v>
+        <v>1.11</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.205</v>
+        <v>0.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="AU15" t="n">
         <v>0.571</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.119</v>
+        <v>0.122</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.174</v>
+        <v>0.17</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="16">
@@ -2691,64 +2691,64 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" t="n">
+        <v>278</v>
+      </c>
+      <c r="D16" t="n">
+        <v>73</v>
+      </c>
+      <c r="E16" t="n">
+        <v>136</v>
+      </c>
+      <c r="F16" t="n">
         <v>28</v>
       </c>
-      <c r="C16" t="n">
-        <v>248</v>
-      </c>
-      <c r="D16" t="n">
-        <v>67</v>
-      </c>
-      <c r="E16" t="n">
-        <v>119</v>
-      </c>
-      <c r="F16" t="n">
-        <v>25</v>
-      </c>
       <c r="G16" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H16" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="J16" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="K16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M16" t="n">
         <v>27</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="Q16" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="R16" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S16" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="T16" t="n">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="U16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V16" t="n">
         <v>33</v>
@@ -2760,31 +2760,31 @@
         <v>6</v>
       </c>
       <c r="Y16" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="Z16" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.702</v>
+        <v>0.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AC16" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.549</v>
+        <v>0.492</v>
       </c>
       <c r="AE16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.462</v>
+        <v>0.483</v>
       </c>
       <c r="AH16" t="n">
         <v>7</v>
@@ -2796,51 +2796,51 @@
         <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.257</v>
+        <v>0.259</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>518:41</t>
+          <t>595:32</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>288.88</v>
+        <v>331.16</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.533</v>
+        <v>0.513</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.858</v>
+        <v>0.839</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.242</v>
+        <v>0.239</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.199</v>
+        <v>0.214</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.043</v>
+        <v>2.139</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.249</v>
+        <v>0.248</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.181</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="17">
@@ -2850,100 +2850,100 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E17" t="n">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="F17" t="n">
         <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H17" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M17" t="n">
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35</v>
+      </c>
+      <c r="R17" t="n">
+        <v>82</v>
+      </c>
+      <c r="S17" t="n">
+        <v>64</v>
+      </c>
+      <c r="T17" t="n">
+        <v>450</v>
+      </c>
+      <c r="U17" t="n">
         <v>30</v>
       </c>
-      <c r="Q17" t="n">
-        <v>30</v>
-      </c>
-      <c r="R17" t="n">
-        <v>71</v>
-      </c>
-      <c r="S17" t="n">
-        <v>55</v>
-      </c>
-      <c r="T17" t="n">
-        <v>405</v>
-      </c>
-      <c r="U17" t="n">
-        <v>27</v>
-      </c>
       <c r="V17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="W17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="Z17" t="n">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF17" t="n">
         <v>26</v>
       </c>
-      <c r="AD17" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>21</v>
-      </c>
       <c r="AG17" t="n">
-        <v>0.476</v>
+        <v>0.462</v>
       </c>
       <c r="AH17" t="n">
         <v>1</v>
@@ -2958,45 +2958,45 @@
         <v>12</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.353</v>
+        <v>0.316</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>469:45</t>
+          <t>534:27</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>256.52</v>
+        <v>291.48</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.674</v>
+        <v>0.676</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.7</v>
+        <v>0.702</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.236</v>
+        <v>1.235</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.229</v>
+        <v>0.233</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.433</v>
+        <v>0.429</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.244</v>
+        <v>0.243</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.146</v>
+        <v>0.134</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.215</v>
+        <v>0.213</v>
       </c>
       <c r="AY17" t="n">
         <v>0.017</v>
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -3030,19 +3030,19 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
@@ -3051,25 +3051,25 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="U18" t="n">
         <v>8</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -3078,31 +3078,31 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="AB18" t="n">
         <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.6</v>
+        <v>0.375</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
       </c>
       <c r="AF18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AH18" t="n">
         <v>1</v>
@@ -3124,41 +3124,41 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>58:24</t>
+          <t>76:47</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>30.96</v>
+        <v>35.84</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.6</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.521</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.872</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.226</v>
+        <v>0.223</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.429</v>
+        <v>2.625</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.237</v>
+        <v>0.208</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.039</v>
+        <v>0.089</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.141</v>
+        <v>0.151</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="19">
@@ -3323,478 +3323,478 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>#37 M. ANDRIC</t>
+          <t>#33 I. CRUZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.708</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.595</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.434</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>545:55</t>
+          <t>03:43</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>183.64</v>
+        <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.658</v>
+        <v>0.75</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.182</v>
+        <v>1</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.131</v>
+        <v>0.333</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.375</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.151</v>
+        <v>0.36</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.047</v>
+        <v>0.305</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>#47 A. KURUCS</t>
+          <t>#37 M. ANDRIC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>176</v>
+        <v>266</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E21" t="n">
+        <v>57</v>
+      </c>
+      <c r="F21" t="n">
+        <v>59</v>
+      </c>
+      <c r="G21" t="n">
+        <v>117</v>
+      </c>
+      <c r="H21" t="n">
+        <v>31</v>
+      </c>
+      <c r="I21" t="n">
+        <v>37</v>
+      </c>
+      <c r="J21" t="n">
+        <v>38</v>
+      </c>
+      <c r="K21" t="n">
+        <v>38</v>
+      </c>
+      <c r="L21" t="n">
+        <v>25</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>27</v>
+      </c>
+      <c r="R21" t="n">
+        <v>62</v>
+      </c>
+      <c r="S21" t="n">
         <v>48</v>
       </c>
-      <c r="F21" t="n">
-        <v>39</v>
-      </c>
-      <c r="G21" t="n">
-        <v>126</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="T21" t="n">
+        <v>264</v>
+      </c>
+      <c r="U21" t="n">
+        <v>44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>35</v>
+      </c>
+      <c r="W21" t="n">
         <v>13</v>
       </c>
-      <c r="I21" t="n">
-        <v>23</v>
-      </c>
-      <c r="J21" t="n">
-        <v>27</v>
-      </c>
-      <c r="K21" t="n">
-        <v>39</v>
-      </c>
-      <c r="L21" t="n">
-        <v>17</v>
-      </c>
-      <c r="M21" t="n">
-        <v>26</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="X21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC21" t="n">
         <v>20</v>
       </c>
-      <c r="Q21" t="n">
-        <v>20</v>
-      </c>
-      <c r="R21" t="n">
-        <v>55</v>
-      </c>
-      <c r="S21" t="n">
-        <v>33</v>
-      </c>
-      <c r="T21" t="n">
-        <v>126</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="AD21" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AH21" t="n">
         <v>29</v>
       </c>
-      <c r="V21" t="n">
-        <v>18</v>
-      </c>
-      <c r="W21" t="n">
-        <v>17</v>
-      </c>
-      <c r="X21" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>16</v>
-      </c>
       <c r="AI21" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.372</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.277</v>
+        <v>0.462</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>591:20</t>
+          <t>638:45</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>204.12</v>
+        <v>217.28</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.468</v>
+        <v>0.675</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.478</v>
+        <v>0.699</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.862</v>
+        <v>1.224</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.098</v>
+        <v>0.124</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.075</v>
+        <v>0.178</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.35</v>
+        <v>1.407</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.032</v>
+        <v>0.044</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.078</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#47 A. KURUCS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K22" t="n">
         <v>46</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R22" t="n">
+        <v>65</v>
+      </c>
+      <c r="S22" t="n">
+        <v>33</v>
+      </c>
+      <c r="T22" t="n">
+        <v>138</v>
+      </c>
+      <c r="U22" t="n">
+        <v>37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>23</v>
+      </c>
+      <c r="W22" t="n">
+        <v>17</v>
+      </c>
+      <c r="X22" t="n">
         <v>7</v>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.646</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>665:23</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>229.12</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="23">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -3831,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3846,19 +3846,19 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -3963,153 +3963,153 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>2523</v>
+        <v>2917</v>
       </c>
       <c r="D24" t="n">
-        <v>591</v>
+        <v>689</v>
       </c>
       <c r="E24" t="n">
-        <v>1059</v>
+        <v>1220</v>
       </c>
       <c r="F24" t="n">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="G24" t="n">
-        <v>802</v>
+        <v>913</v>
       </c>
       <c r="H24" t="n">
-        <v>462</v>
+        <v>531</v>
       </c>
       <c r="I24" t="n">
-        <v>586</v>
+        <v>674</v>
       </c>
       <c r="J24" t="n">
-        <v>493</v>
+        <v>583</v>
       </c>
       <c r="K24" t="n">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="L24" t="n">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="M24" t="n">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="N24" t="n">
+        <v>175</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>412</v>
+      </c>
+      <c r="R24" t="n">
+        <v>756</v>
+      </c>
+      <c r="S24" t="n">
+        <v>707</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3288</v>
+      </c>
+      <c r="U24" t="n">
+        <v>414</v>
+      </c>
+      <c r="V24" t="n">
+        <v>383</v>
+      </c>
+      <c r="W24" t="n">
+        <v>152</v>
+      </c>
+      <c r="X24" t="n">
+        <v>87</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>954</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1258</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="AB24" t="n">
         <v>154</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>383</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>358</v>
-      </c>
-      <c r="R24" t="n">
-        <v>664</v>
-      </c>
-      <c r="S24" t="n">
-        <v>620</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2821</v>
-      </c>
-      <c r="U24" t="n">
-        <v>363</v>
-      </c>
-      <c r="V24" t="n">
-        <v>351</v>
-      </c>
-      <c r="W24" t="n">
-        <v>134</v>
-      </c>
-      <c r="X24" t="n">
-        <v>75</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>835</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1110</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
+        <v>353</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>112</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>283</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="AH24" t="n">
         <v>125</v>
       </c>
-      <c r="AC24" t="n">
-        <v>294</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>93</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>241</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>111</v>
-      </c>
       <c r="AI24" t="n">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="AK24" t="n">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="AL24" t="n">
-        <v>556</v>
+        <v>635</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.327</v>
+        <v>0.332</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>2501.84</v>
+        <v>2867.56</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.554</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.595</v>
+        <v>0.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.008</v>
+        <v>1.017</v>
       </c>
       <c r="AS24" t="n">
         <v>0.153</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.248</v>
+        <v>0.249</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.287</v>
+        <v>1.331</v>
       </c>
       <c r="AV24" t="n">
         <v>0.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -4122,153 +4122,153 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
-        <v>2603</v>
+        <v>2975</v>
       </c>
       <c r="D25" t="n">
-        <v>584</v>
+        <v>676</v>
       </c>
       <c r="E25" t="n">
-        <v>1005</v>
+        <v>1157</v>
       </c>
       <c r="F25" t="n">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="G25" t="n">
-        <v>798</v>
+        <v>915</v>
       </c>
       <c r="H25" t="n">
-        <v>493</v>
+        <v>561</v>
       </c>
       <c r="I25" t="n">
-        <v>669</v>
+        <v>766</v>
       </c>
       <c r="J25" t="n">
-        <v>536</v>
+        <v>629</v>
       </c>
       <c r="K25" t="n">
-        <v>642</v>
+        <v>739</v>
       </c>
       <c r="L25" t="n">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="M25" t="n">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="N25" t="n">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>401</v>
+        <v>464</v>
       </c>
       <c r="Q25" t="n">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="R25" t="n">
-        <v>625</v>
+        <v>713</v>
       </c>
       <c r="S25" t="n">
-        <v>653</v>
+        <v>745</v>
       </c>
       <c r="T25" t="n">
-        <v>3041</v>
+        <v>3478</v>
       </c>
       <c r="U25" t="n">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="V25" t="n">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="W25" t="n">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="X25" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="Y25" t="n">
-        <v>896</v>
+        <v>1036</v>
       </c>
       <c r="Z25" t="n">
-        <v>1222</v>
+        <v>1409</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="AB25" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="AC25" t="n">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.43</v>
+        <v>0.427</v>
       </c>
       <c r="AE25" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AF25" t="n">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.365</v>
+        <v>0.345</v>
       </c>
       <c r="AH25" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="AI25" t="n">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.414</v>
+        <v>0.404</v>
       </c>
       <c r="AK25" t="n">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="AL25" t="n">
-        <v>561</v>
+        <v>643</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.385</v>
+        <v>0.379</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>2498.36</v>
+        <v>2873.04</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.585</v>
+        <v>0.583</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.621</v>
+        <v>0.617</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.042</v>
+        <v>1.035</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.273</v>
+        <v>0.271</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.337</v>
+        <v>1.356</v>
       </c>
       <c r="AV25" t="n">
         <v>0.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.129</v>
+        <v>0.131</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -4338,156 +4338,156 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>6.769</v>
+        <v>6.733</v>
       </c>
       <c r="D27" t="n">
-        <v>1.731</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
-        <v>2.962</v>
+        <v>3.067</v>
       </c>
       <c r="F27" t="n">
-        <v>0.654</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>2.192</v>
+        <v>2.033</v>
       </c>
       <c r="H27" t="n">
-        <v>1.346</v>
+        <v>1.433</v>
       </c>
       <c r="I27" t="n">
-        <v>1.808</v>
+        <v>1.867</v>
       </c>
       <c r="J27" t="n">
-        <v>0.538</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>1.769</v>
+        <v>1.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.615</v>
+        <v>1.667</v>
       </c>
       <c r="M27" t="n">
-        <v>0.962</v>
+        <v>1.033</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5</v>
+        <v>2.367</v>
       </c>
       <c r="S27" t="n">
-        <v>1.346</v>
+        <v>1.467</v>
       </c>
       <c r="T27" t="n">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="V27" t="n">
-        <v>1.538</v>
+        <v>1.567</v>
       </c>
       <c r="W27" t="n">
-        <v>0.885</v>
+        <v>0.767</v>
       </c>
       <c r="X27" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.769</v>
+        <v>2.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.923</v>
+        <v>3.967</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.706</v>
+        <v>0.731</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.308</v>
+        <v>0.333</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.767</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.444</v>
+        <v>0.435</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.462</v>
+        <v>0.4</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.308</v>
+        <v>1.167</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.353</v>
+        <v>0.343</v>
       </c>
       <c r="AK27" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="AM27" t="n">
         <v>0.192</v>
       </c>
-      <c r="AL27" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.217</v>
-      </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>6.411</v>
+        <v>6.421</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.526</v>
+        <v>0.52</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.569</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.056</v>
+        <v>1.049</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.261</v>
+        <v>0.281</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.167</v>
+        <v>1.133</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.169</v>
+        <v>0.171</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.107</v>
+        <v>0.113</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.123</v>
+        <v>0.125</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="28">
@@ -4497,156 +4497,156 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>10.741</v>
+        <v>10.839</v>
       </c>
       <c r="D28" t="n">
-        <v>1.704</v>
+        <v>1.774</v>
       </c>
       <c r="E28" t="n">
-        <v>3.37</v>
+        <v>3.355</v>
       </c>
       <c r="F28" t="n">
-        <v>1.444</v>
+        <v>1.484</v>
       </c>
       <c r="G28" t="n">
-        <v>3.815</v>
+        <v>3.677</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2.839</v>
       </c>
       <c r="I28" t="n">
-        <v>3.185</v>
+        <v>3.032</v>
       </c>
       <c r="J28" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.097</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.968</v>
+      </c>
+      <c r="T28" t="n">
+        <v>361</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>4.065</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.677</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.452</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AO28" t="n">
+        <v>9.754</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="AR28" t="n">
         <v>1.111</v>
       </c>
-      <c r="K28" t="n">
-        <v>2.741</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.296</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.296</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.037</v>
-      </c>
-      <c r="T28" t="n">
-        <v>309</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.185</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>4.222</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.889</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0.963</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>20:08</t>
-        </is>
-      </c>
-      <c r="AO28" t="n">
-        <v>9.882999999999999</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.087</v>
-      </c>
       <c r="AS28" t="n">
-        <v>0.131</v>
+        <v>0.142</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.418</v>
+        <v>0.404</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.857</v>
+        <v>0.767</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.22</v>
+        <v>0.217</v>
       </c>
       <c r="AW28" t="n">
         <v>0.029</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="29">
@@ -4656,22 +4656,22 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -4692,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4704,99 +4704,99 @@
         <v>2</v>
       </c>
       <c r="R29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL29" t="n">
         <v>2</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1</v>
-      </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.5</v>
+        <v>0.308</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.287</v>
+        <v>0.294</v>
       </c>
       <c r="AW29" t="n">
         <v>0</v>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.032</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="30">
@@ -4815,156 +4815,156 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>9.385</v>
+        <v>9.241</v>
       </c>
       <c r="D30" t="n">
-        <v>2.846</v>
+        <v>2.828</v>
       </c>
       <c r="E30" t="n">
-        <v>6.346</v>
+        <v>6.207</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="G30" t="n">
-        <v>2.615</v>
+        <v>2.586</v>
       </c>
       <c r="H30" t="n">
-        <v>1.269</v>
+        <v>1.207</v>
       </c>
       <c r="I30" t="n">
-        <v>1.692</v>
+        <v>1.586</v>
       </c>
       <c r="J30" t="n">
-        <v>5.038</v>
+        <v>5.207</v>
       </c>
       <c r="K30" t="n">
-        <v>0.962</v>
+        <v>0.931</v>
       </c>
       <c r="L30" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="M30" t="n">
-        <v>0.962</v>
+        <v>0.966</v>
       </c>
       <c r="N30" t="n">
-        <v>0.462</v>
+        <v>0.414</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.231</v>
+        <v>2.207</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.231</v>
+        <v>2.207</v>
       </c>
       <c r="R30" t="n">
-        <v>2.577</v>
+        <v>2.517</v>
       </c>
       <c r="S30" t="n">
-        <v>2.538</v>
+        <v>2.414</v>
       </c>
       <c r="T30" t="n">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.345</v>
       </c>
       <c r="V30" t="n">
-        <v>0.962</v>
+        <v>0.931</v>
       </c>
       <c r="W30" t="n">
-        <v>0.385</v>
+        <v>0.414</v>
       </c>
       <c r="X30" t="n">
-        <v>0.192</v>
+        <v>0.207</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.577</v>
+        <v>2.414</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.962</v>
+        <v>3.655</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.654</v>
+        <v>0.724</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>2.103</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.327</v>
+        <v>0.344</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.885</v>
+        <v>0.897</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.077</v>
+        <v>2.034</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.426</v>
+        <v>0.441</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.077</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.308</v>
+        <v>0.276</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.731</v>
+        <v>0.724</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.308</v>
+        <v>2.31</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.317</v>
+        <v>0.313</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>11.937</v>
+        <v>11.698</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.453</v>
+        <v>0.457</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.483</v>
+        <v>0.487</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.786</v>
+        <v>0.79</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.187</v>
+        <v>0.189</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.142</v>
+        <v>0.137</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.259</v>
+        <v>2.359</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.252</v>
+        <v>0.25</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="31">
@@ -4974,100 +4974,100 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>3.071</v>
+        <v>4.25</v>
       </c>
       <c r="D31" t="n">
-        <v>1.25</v>
+        <v>1.688</v>
       </c>
       <c r="E31" t="n">
-        <v>2.036</v>
+        <v>2.719</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="H31" t="n">
-        <v>0.571</v>
+        <v>0.875</v>
       </c>
       <c r="I31" t="n">
-        <v>1.107</v>
+        <v>1.594</v>
       </c>
       <c r="J31" t="n">
-        <v>0.321</v>
+        <v>0.438</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>1.188</v>
       </c>
       <c r="L31" t="n">
-        <v>0.643</v>
+        <v>0.719</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.219</v>
       </c>
       <c r="N31" t="n">
-        <v>0.214</v>
+        <v>0.312</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="R31" t="n">
-        <v>1.929</v>
+        <v>1.969</v>
       </c>
       <c r="S31" t="n">
-        <v>1.107</v>
+        <v>1.469</v>
       </c>
       <c r="T31" t="n">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="U31" t="n">
-        <v>0.429</v>
+        <v>0.531</v>
       </c>
       <c r="V31" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
       <c r="W31" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="X31" t="n">
-        <v>0.036</v>
+        <v>0.094</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.536</v>
+        <v>2.156</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.393</v>
+        <v>3.312</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.642</v>
+        <v>0.651</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.25</v>
+        <v>0.344</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.607</v>
+        <v>0.781</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.412</v>
+        <v>0.44</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.036</v>
+        <v>0.062</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.143</v>
+        <v>0.219</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5082,48 +5082,48 @@
         <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="AM31" t="n">
         <v>0</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>3.13</v>
+        <v>4.076</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.603</v>
+        <v>0.614</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.6</v>
+        <v>0.616</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.981</v>
+        <v>1.043</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.183</v>
+        <v>0.153</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.276</v>
+        <v>0.318</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.162</v>
+        <v>0.182</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="32">
@@ -5133,153 +5133,153 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>14.286</v>
+        <v>13.969</v>
       </c>
       <c r="D32" t="n">
-        <v>1.929</v>
+        <v>1.938</v>
       </c>
       <c r="E32" t="n">
-        <v>3.786</v>
+        <v>3.781</v>
       </c>
       <c r="F32" t="n">
-        <v>2.071</v>
+        <v>2.062</v>
       </c>
       <c r="G32" t="n">
-        <v>5.036</v>
+        <v>5.125</v>
       </c>
       <c r="H32" t="n">
-        <v>4.214</v>
+        <v>3.906</v>
       </c>
       <c r="I32" t="n">
-        <v>4.714</v>
+        <v>4.344</v>
       </c>
       <c r="J32" t="n">
-        <v>1.393</v>
+        <v>1.438</v>
       </c>
       <c r="K32" t="n">
-        <v>1.464</v>
+        <v>1.469</v>
       </c>
       <c r="L32" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.844</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.281</v>
+      </c>
+      <c r="T32" t="n">
+        <v>456</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="X32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M32" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.464</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.464</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.857</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4.393</v>
-      </c>
-      <c r="T32" t="n">
-        <v>407</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.393</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.464</v>
-      </c>
       <c r="Y32" t="n">
-        <v>5.25</v>
+        <v>4.906</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.357</v>
+        <v>5.938</v>
       </c>
       <c r="AA32" t="n">
         <v>0.826</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.143</v>
+        <v>1.188</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.438</v>
+        <v>0.447</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
       <c r="AF32" t="n">
         <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.429</v>
+        <v>0.469</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.143</v>
+        <v>1.188</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.375</v>
+        <v>0.395</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.643</v>
+        <v>1.594</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.893</v>
+        <v>3.938</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.422</v>
+        <v>0.405</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>12.36</v>
+        <v>12.286</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.571</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.656</v>
+        <v>0.646</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.156</v>
+        <v>1.137</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.118</v>
+        <v>0.12</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.478</v>
+        <v>0.439</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.951</v>
+        <v>0.979</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.254</v>
+        <v>0.25</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="AY32" t="n">
         <v>0.051</v>
@@ -5292,43 +5292,43 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>6.679</v>
+        <v>7.156</v>
       </c>
       <c r="D33" t="n">
-        <v>1.286</v>
+        <v>1.344</v>
       </c>
       <c r="E33" t="n">
-        <v>2.679</v>
+        <v>2.656</v>
       </c>
       <c r="F33" t="n">
-        <v>1.107</v>
+        <v>1.156</v>
       </c>
       <c r="G33" t="n">
-        <v>3.143</v>
+        <v>3.125</v>
       </c>
       <c r="H33" t="n">
-        <v>0.786</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.929</v>
+        <v>1.156</v>
       </c>
       <c r="J33" t="n">
-        <v>0.679</v>
+        <v>0.906</v>
       </c>
       <c r="K33" t="n">
-        <v>3.357</v>
+        <v>3.469</v>
       </c>
       <c r="L33" t="n">
-        <v>1.179</v>
+        <v>1.094</v>
       </c>
       <c r="M33" t="n">
-        <v>0.893</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>0.25</v>
+        <v>0.219</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5340,108 +5340,108 @@
         <v>0.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.964</v>
+        <v>2.031</v>
       </c>
       <c r="S33" t="n">
-        <v>0.857</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="T33" t="n">
-        <v>220</v>
+        <v>276</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.469</v>
       </c>
       <c r="V33" t="n">
-        <v>0.786</v>
+        <v>0.781</v>
       </c>
       <c r="W33" t="n">
-        <v>0.607</v>
+        <v>0.531</v>
       </c>
       <c r="X33" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.357</v>
+        <v>1.594</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.714</v>
+        <v>1.969</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.792</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.179</v>
+        <v>0.219</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.536</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.333</v>
+        <v>0.389</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.536</v>
+        <v>0.531</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.357</v>
+        <v>1.281</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.395</v>
+        <v>0.415</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.714</v>
+        <v>0.719</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.357</v>
+        <v>1.406</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.526</v>
+        <v>0.511</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.393</v>
+        <v>0.438</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.786</v>
+        <v>1.719</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.22</v>
+        <v>0.255</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.73</v>
+        <v>6.79</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.506</v>
+        <v>0.532</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.536</v>
+        <v>0.569</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.992</v>
+        <v>1.054</v>
       </c>
       <c r="AS33" t="n">
         <v>0.074</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.135</v>
+        <v>0.173</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.357</v>
+        <v>1.812</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.142</v>
+        <v>0.144</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.186</v>
+        <v>0.191</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.023</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="34">
@@ -5451,16 +5451,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C34" t="n">
-        <v>5.357</v>
+        <v>5.345</v>
       </c>
       <c r="D34" t="n">
-        <v>2.143</v>
+        <v>2.138</v>
       </c>
       <c r="E34" t="n">
-        <v>3.179</v>
+        <v>3.138</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -5469,79 +5469,79 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.071</v>
+        <v>1.069</v>
       </c>
       <c r="I34" t="n">
-        <v>1.607</v>
+        <v>1.621</v>
       </c>
       <c r="J34" t="n">
-        <v>0.571</v>
+        <v>0.552</v>
       </c>
       <c r="K34" t="n">
-        <v>2.25</v>
+        <v>2.207</v>
       </c>
       <c r="L34" t="n">
-        <v>1.607</v>
+        <v>1.621</v>
       </c>
       <c r="M34" t="n">
-        <v>0.464</v>
+        <v>0.448</v>
       </c>
       <c r="N34" t="n">
-        <v>0.643</v>
+        <v>0.621</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="R34" t="n">
-        <v>2.536</v>
+        <v>2.621</v>
       </c>
       <c r="S34" t="n">
-        <v>2.036</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="U34" t="n">
-        <v>0.607</v>
+        <v>0.655</v>
       </c>
       <c r="V34" t="n">
-        <v>1.143</v>
+        <v>1.207</v>
       </c>
       <c r="W34" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="X34" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.679</v>
+        <v>3.621</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.748</v>
+        <v>0.743</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.429</v>
+        <v>0.483</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.893</v>
+        <v>0.931</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.48</v>
+        <v>0.519</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.214</v>
+        <v>0.207</v>
       </c>
       <c r="AG34" t="n">
         <v>0.167</v>
@@ -5566,41 +5566,41 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>4.886</v>
+        <v>4.817</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.674</v>
+        <v>0.681</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.096</v>
+        <v>1.11</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.205</v>
+        <v>0.2</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="AU34" t="n">
         <v>0.571</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.119</v>
+        <v>0.122</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.174</v>
+        <v>0.17</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="35">
@@ -5610,156 +5610,156 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C35" t="n">
-        <v>8.856999999999999</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>2.393</v>
+        <v>2.281</v>
       </c>
       <c r="E35" t="n">
         <v>4.25</v>
       </c>
       <c r="F35" t="n">
-        <v>0.893</v>
+        <v>0.875</v>
       </c>
       <c r="G35" t="n">
         <v>2.75</v>
       </c>
       <c r="H35" t="n">
-        <v>1.393</v>
+        <v>1.5</v>
       </c>
       <c r="I35" t="n">
-        <v>1.857</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>5.107</v>
+        <v>5.281</v>
       </c>
       <c r="K35" t="n">
-        <v>1.357</v>
+        <v>1.312</v>
       </c>
       <c r="L35" t="n">
-        <v>0.786</v>
+        <v>0.75</v>
       </c>
       <c r="M35" t="n">
-        <v>0.964</v>
+        <v>0.844</v>
       </c>
       <c r="N35" t="n">
-        <v>0.179</v>
+        <v>0.219</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>2.469</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.5</v>
+        <v>2.469</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.438</v>
       </c>
       <c r="S35" t="n">
-        <v>2.107</v>
+        <v>2.125</v>
       </c>
       <c r="T35" t="n">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="U35" t="n">
-        <v>0.786</v>
+        <v>0.75</v>
       </c>
       <c r="V35" t="n">
-        <v>1.179</v>
+        <v>1.031</v>
       </c>
       <c r="W35" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="X35" t="n">
-        <v>0.214</v>
+        <v>0.188</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.357</v>
+        <v>2.406</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.357</v>
+        <v>3.438</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.702</v>
+        <v>0.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.821</v>
+        <v>1.906</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.549</v>
+        <v>0.492</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.429</v>
+        <v>0.438</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.929</v>
+        <v>0.906</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.462</v>
+        <v>0.483</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.25</v>
+        <v>0.219</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.25</v>
+        <v>0.219</v>
       </c>
       <c r="AJ35" t="n">
         <v>1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.643</v>
+        <v>0.656</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.5</v>
+        <v>2.531</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.257</v>
+        <v>0.259</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>10.317</v>
+        <v>10.349</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.533</v>
+        <v>0.513</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.858</v>
+        <v>0.839</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.242</v>
+        <v>0.239</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.199</v>
+        <v>0.214</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.043</v>
+        <v>2.139</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.249</v>
+        <v>0.248</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.181</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="36">
@@ -5769,153 +5769,153 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>11.321</v>
+        <v>11.25</v>
       </c>
       <c r="D36" t="n">
-        <v>4.143</v>
+        <v>4.188</v>
       </c>
       <c r="E36" t="n">
-        <v>5.893</v>
+        <v>5.844</v>
       </c>
       <c r="F36" t="n">
-        <v>0.464</v>
+        <v>0.406</v>
       </c>
       <c r="G36" t="n">
-        <v>1.286</v>
+        <v>1.25</v>
       </c>
       <c r="H36" t="n">
-        <v>1.643</v>
+        <v>1.656</v>
       </c>
       <c r="I36" t="n">
-        <v>2.071</v>
+        <v>2.094</v>
       </c>
       <c r="J36" t="n">
-        <v>0.464</v>
+        <v>0.469</v>
       </c>
       <c r="K36" t="n">
-        <v>3.071</v>
+        <v>3.062</v>
       </c>
       <c r="L36" t="n">
-        <v>2.179</v>
+        <v>1.969</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5</v>
+        <v>0.438</v>
       </c>
       <c r="N36" t="n">
-        <v>1.571</v>
+        <v>1.469</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.071</v>
+        <v>1.094</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.071</v>
+        <v>1.094</v>
       </c>
       <c r="R36" t="n">
-        <v>2.536</v>
+        <v>2.562</v>
       </c>
       <c r="S36" t="n">
-        <v>1.964</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>405</v>
+        <v>450</v>
       </c>
       <c r="U36" t="n">
-        <v>0.964</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>2.607</v>
+        <v>2.406</v>
       </c>
       <c r="W36" t="n">
-        <v>0.143</v>
+        <v>0.188</v>
       </c>
       <c r="X36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="Y36" t="n">
-        <v>5.071</v>
+        <v>5</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.286</v>
+        <v>6.125</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.357</v>
+        <v>0.469</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.929</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.385</v>
+        <v>0.469</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.357</v>
+        <v>0.375</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.75</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.476</v>
+        <v>0.462</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.5</v>
       </c>
       <c r="AK36" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AO36" t="n">
+        <v>9.109</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AU36" t="n">
         <v>0.429</v>
       </c>
-      <c r="AL36" t="n">
-        <v>1.214</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AO36" t="n">
-        <v>9.161</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.236</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0.433</v>
-      </c>
       <c r="AV36" t="n">
-        <v>0.244</v>
+        <v>0.243</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.146</v>
+        <v>0.134</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.215</v>
+        <v>0.213</v>
       </c>
       <c r="AY36" t="n">
         <v>0.017</v>
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="E37" t="n">
-        <v>0.519</v>
+        <v>0.548</v>
       </c>
       <c r="F37" t="n">
-        <v>0.074</v>
+        <v>0.065</v>
       </c>
       <c r="G37" t="n">
-        <v>0.222</v>
+        <v>0.194</v>
       </c>
       <c r="H37" t="n">
-        <v>0.111</v>
+        <v>0.097</v>
       </c>
       <c r="I37" t="n">
-        <v>0.333</v>
+        <v>0.355</v>
       </c>
       <c r="J37" t="n">
-        <v>0.63</v>
+        <v>0.677</v>
       </c>
       <c r="K37" t="n">
-        <v>0.259</v>
+        <v>0.323</v>
       </c>
       <c r="L37" t="n">
-        <v>0.074</v>
+        <v>0.194</v>
       </c>
       <c r="M37" t="n">
-        <v>0.111</v>
+        <v>0.129</v>
       </c>
       <c r="N37" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.259</v>
+        <v>0.258</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.259</v>
+        <v>0.258</v>
       </c>
       <c r="R37" t="n">
-        <v>0.407</v>
+        <v>0.452</v>
       </c>
       <c r="S37" t="n">
-        <v>0.407</v>
+        <v>0.419</v>
       </c>
       <c r="T37" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="U37" t="n">
-        <v>0.296</v>
+        <v>0.258</v>
       </c>
       <c r="V37" t="n">
-        <v>0.074</v>
+        <v>0.129</v>
       </c>
       <c r="W37" t="n">
-        <v>0.074</v>
+        <v>0.065</v>
       </c>
       <c r="X37" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.481</v>
+        <v>0.452</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.111</v>
+        <v>0.097</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.185</v>
+        <v>0.258</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.6</v>
+        <v>0.375</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.111</v>
+        <v>0.097</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.185</v>
+        <v>0.194</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.111</v>
+        <v>0.097</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.333</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.111</v>
+        <v>0.097</v>
       </c>
       <c r="AM37" t="n">
         <v>0.333</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>02:09</t>
+          <t>02:28</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>1.147</v>
+        <v>1.156</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.6</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.521</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.872</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.226</v>
+        <v>0.223</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.429</v>
+        <v>2.625</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.237</v>
+        <v>0.208</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.039</v>
+        <v>0.089</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.141</v>
+        <v>0.151</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="38">
@@ -6236,484 +6236,484 @@
         <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#37 M. ANDRIC (Per Game)</t>
+          <t>#33 I. CRUZ (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>8.68</v>
+        <v>1.5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.92</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R39" t="n">
         <v>1</v>
       </c>
-      <c r="I39" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.2</v>
-      </c>
       <c r="S39" t="n">
-        <v>1.68</v>
+        <v>0.5</v>
       </c>
       <c r="T39" t="n">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.708</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="AO39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
         <v>0.36</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>21:50</t>
-        </is>
-      </c>
-      <c r="AO39" t="n">
-        <v>7.346</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.182</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0.151</v>
-      </c>
       <c r="AW39" t="n">
-        <v>0.047</v>
+        <v>0.305</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#47 A. KURUCS (Per Game)</t>
+          <t>#37 M. ANDRIC (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C40" t="n">
-        <v>6.286</v>
+        <v>9.172000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.821</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1.714</v>
+        <v>1.966</v>
       </c>
       <c r="F40" t="n">
-        <v>1.393</v>
+        <v>2.034</v>
       </c>
       <c r="G40" t="n">
-        <v>4.5</v>
+        <v>4.034</v>
       </c>
       <c r="H40" t="n">
-        <v>0.464</v>
+        <v>1.069</v>
       </c>
       <c r="I40" t="n">
-        <v>0.821</v>
+        <v>1.276</v>
       </c>
       <c r="J40" t="n">
-        <v>0.964</v>
+        <v>1.31</v>
       </c>
       <c r="K40" t="n">
-        <v>1.393</v>
+        <v>1.31</v>
       </c>
       <c r="L40" t="n">
-        <v>0.607</v>
+        <v>0.862</v>
       </c>
       <c r="M40" t="n">
-        <v>0.929</v>
+        <v>0.759</v>
       </c>
       <c r="N40" t="n">
-        <v>0.179</v>
+        <v>0.276</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.714</v>
+        <v>0.931</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.714</v>
+        <v>0.931</v>
       </c>
       <c r="R40" t="n">
-        <v>1.964</v>
+        <v>2.138</v>
       </c>
       <c r="S40" t="n">
-        <v>1.179</v>
+        <v>1.655</v>
       </c>
       <c r="T40" t="n">
-        <v>126</v>
+        <v>264</v>
       </c>
       <c r="U40" t="n">
-        <v>1.036</v>
+        <v>1.517</v>
       </c>
       <c r="V40" t="n">
-        <v>0.643</v>
+        <v>1.207</v>
       </c>
       <c r="W40" t="n">
-        <v>0.607</v>
+        <v>0.448</v>
       </c>
       <c r="X40" t="n">
-        <v>0.25</v>
+        <v>0.276</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.036</v>
+        <v>1.414</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.643</v>
+        <v>1.897</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.63</v>
+        <v>0.745</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.143</v>
+        <v>0.379</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.429</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.333</v>
+        <v>0.55</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.107</v>
+        <v>0.276</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.464</v>
+        <v>0.655</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.231</v>
+        <v>0.421</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.536</v>
+        <v>1.793</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.372</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.821</v>
+        <v>1.034</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.964</v>
+        <v>2.241</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.277</v>
+        <v>0.462</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>7.29</v>
+        <v>7.492</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.468</v>
+        <v>0.675</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.478</v>
+        <v>0.699</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.862</v>
+        <v>1.224</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.098</v>
+        <v>0.124</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.075</v>
+        <v>0.178</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.35</v>
+        <v>1.407</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.032</v>
+        <v>0.044</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.078</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.033</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#47 A. KURUCS (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>6.125</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1.781</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1.344</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>4.312</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1.643</v>
+        <v>1.438</v>
       </c>
       <c r="L41" t="n">
-        <v>1.821</v>
+        <v>0.594</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.893</v>
+        <v>0.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R41" t="n">
-        <v>0.25</v>
+        <v>2.031</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.156</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>0.646</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2.812</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="42">
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -6750,10 +6750,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1.812</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -6765,19 +6765,19 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>0.893</v>
+        <v>0</v>
       </c>
       <c r="AP42" t="n">
         <v>0</v>
@@ -6882,118 +6882,118 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C43" t="n">
-        <v>90.107</v>
+        <v>91.15600000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>21.107</v>
+        <v>21.531</v>
       </c>
       <c r="E43" t="n">
-        <v>37.821</v>
+        <v>38.125</v>
       </c>
       <c r="F43" t="n">
-        <v>10.464</v>
+        <v>10.5</v>
       </c>
       <c r="G43" t="n">
-        <v>28.643</v>
+        <v>28.531</v>
       </c>
       <c r="H43" t="n">
-        <v>16.5</v>
+        <v>16.594</v>
       </c>
       <c r="I43" t="n">
-        <v>20.929</v>
+        <v>21.062</v>
       </c>
       <c r="J43" t="n">
-        <v>17.607</v>
+        <v>18.219</v>
       </c>
       <c r="K43" t="n">
-        <v>21.964</v>
+        <v>22.406</v>
       </c>
       <c r="L43" t="n">
-        <v>12.571</v>
+        <v>12.219</v>
       </c>
       <c r="M43" t="n">
-        <v>7.571</v>
+        <v>7.594</v>
       </c>
       <c r="N43" t="n">
-        <v>5.5</v>
+        <v>5.469</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>13.679</v>
+        <v>13.688</v>
       </c>
       <c r="Q43" t="n">
-        <v>12.786</v>
+        <v>12.875</v>
       </c>
       <c r="R43" t="n">
-        <v>23.714</v>
+        <v>23.625</v>
       </c>
       <c r="S43" t="n">
-        <v>22.143</v>
+        <v>22.094</v>
       </c>
       <c r="T43" t="n">
-        <v>2821</v>
+        <v>3288</v>
       </c>
       <c r="U43" t="n">
-        <v>12.964</v>
+        <v>12.938</v>
       </c>
       <c r="V43" t="n">
-        <v>12.536</v>
+        <v>11.969</v>
       </c>
       <c r="W43" t="n">
-        <v>4.786</v>
+        <v>4.75</v>
       </c>
       <c r="X43" t="n">
-        <v>2.679</v>
+        <v>2.719</v>
       </c>
       <c r="Y43" t="n">
-        <v>29.821</v>
+        <v>29.812</v>
       </c>
       <c r="Z43" t="n">
-        <v>39.643</v>
+        <v>39.312</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.752</v>
+        <v>0.758</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.464</v>
+        <v>4.812</v>
       </c>
       <c r="AC43" t="n">
-        <v>10.5</v>
+        <v>11.031</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.425</v>
+        <v>0.436</v>
       </c>
       <c r="AE43" t="n">
-        <v>3.321</v>
+        <v>3.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>8.606999999999999</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.386</v>
+        <v>0.396</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.964</v>
+        <v>3.906</v>
       </c>
       <c r="AI43" t="n">
-        <v>8.786</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="AK43" t="n">
-        <v>6.5</v>
+        <v>6.594</v>
       </c>
       <c r="AL43" t="n">
-        <v>19.857</v>
+        <v>19.844</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.327</v>
+        <v>0.332</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
@@ -7001,34 +7001,34 @@
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>89.351</v>
+        <v>89.611</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.554</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.595</v>
+        <v>0.6</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.008</v>
+        <v>1.017</v>
       </c>
       <c r="AS43" t="n">
         <v>0.153</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.248</v>
+        <v>0.249</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.287</v>
+        <v>1.331</v>
       </c>
       <c r="AV43" t="n">
         <v>0.2</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -7041,118 +7041,118 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C44" t="n">
-        <v>92.964</v>
+        <v>92.96899999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>20.857</v>
+        <v>21.125</v>
       </c>
       <c r="E44" t="n">
-        <v>35.893</v>
+        <v>36.156</v>
       </c>
       <c r="F44" t="n">
-        <v>11.214</v>
+        <v>11.062</v>
       </c>
       <c r="G44" t="n">
-        <v>28.5</v>
+        <v>28.594</v>
       </c>
       <c r="H44" t="n">
-        <v>17.607</v>
+        <v>17.531</v>
       </c>
       <c r="I44" t="n">
-        <v>23.893</v>
+        <v>23.938</v>
       </c>
       <c r="J44" t="n">
-        <v>19.143</v>
+        <v>19.656</v>
       </c>
       <c r="K44" t="n">
-        <v>22.929</v>
+        <v>23.094</v>
       </c>
       <c r="L44" t="n">
-        <v>12.071</v>
+        <v>12.062</v>
       </c>
       <c r="M44" t="n">
-        <v>8.036</v>
+        <v>7.938</v>
       </c>
       <c r="N44" t="n">
-        <v>5.393</v>
+        <v>5.438</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>14.321</v>
+        <v>14.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.429</v>
+        <v>13.656</v>
       </c>
       <c r="R44" t="n">
-        <v>22.321</v>
+        <v>22.281</v>
       </c>
       <c r="S44" t="n">
-        <v>23.321</v>
+        <v>23.281</v>
       </c>
       <c r="T44" t="n">
-        <v>3041</v>
+        <v>3478</v>
       </c>
       <c r="U44" t="n">
-        <v>12.214</v>
+        <v>12.094</v>
       </c>
       <c r="V44" t="n">
-        <v>12.679</v>
+        <v>12.281</v>
       </c>
       <c r="W44" t="n">
-        <v>6.071</v>
+        <v>6.344</v>
       </c>
       <c r="X44" t="n">
-        <v>3.714</v>
+        <v>3.875</v>
       </c>
       <c r="Y44" t="n">
-        <v>32</v>
+        <v>32.375</v>
       </c>
       <c r="Z44" t="n">
-        <v>43.643</v>
+        <v>44.031</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.821</v>
+        <v>3.844</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.893000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.43</v>
+        <v>0.427</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.643</v>
+        <v>2.438</v>
       </c>
       <c r="AF44" t="n">
-        <v>7.25</v>
+        <v>7.062</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.365</v>
+        <v>0.345</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.5</v>
+        <v>3.438</v>
       </c>
       <c r="AI44" t="n">
-        <v>8.464</v>
+        <v>8.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.414</v>
+        <v>0.404</v>
       </c>
       <c r="AK44" t="n">
-        <v>7.714</v>
+        <v>7.625</v>
       </c>
       <c r="AL44" t="n">
-        <v>20.036</v>
+        <v>20.094</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.385</v>
+        <v>0.379</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
@@ -7160,25 +7160,25 @@
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>89.227</v>
+        <v>89.782</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.585</v>
+        <v>0.583</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.621</v>
+        <v>0.617</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.042</v>
+        <v>1.035</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.273</v>
+        <v>0.271</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.337</v>
+        <v>1.356</v>
       </c>
       <c r="AV44" t="n">
         <v>0.2</v>
@@ -7187,7 +7187,7 @@
         <v>0.068</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Río Breogán.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Río Breogán.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2476.559999999999</v>
+        <v>2626.599999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2481.8</v>
+        <v>2632.94</v>
       </c>
       <c r="D2" t="n">
-        <v>117.5356596019018</v>
+        <v>117.5112231953634</v>
       </c>
       <c r="E2" t="n">
-        <v>119.8726730598759</v>
+        <v>120.4357106504516</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5593061415846226</v>
+        <v>0.5605926581158779</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1527430986622773</v>
+        <v>0.1520937582301817</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3460176991150443</v>
+        <v>0.3410788381742739</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2489451476793249</v>
+        <v>0.2472357363998231</v>
       </c>
       <c r="J2" t="n">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="K2" t="n">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="L2" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="N2" t="n">
-        <v>954</v>
+        <v>998</v>
       </c>
       <c r="O2" t="n">
-        <v>1258</v>
+        <v>1324</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5897796530707923</v>
+        <v>0.5855816010614773</v>
       </c>
       <c r="Q2" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="R2" t="n">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1654946085325832</v>
+        <v>0.1658558160106148</v>
       </c>
       <c r="T2" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="U2" t="n">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1326769807782466</v>
+        <v>0.1362229102167183</v>
       </c>
       <c r="W2" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="X2" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1303328645100797</v>
+        <v>0.1278195488721804</v>
       </c>
       <c r="Z2" t="n">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="AA2" t="n">
-        <v>635</v>
+        <v>680</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2977027660571964</v>
+        <v>0.3007518796992481</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7583465818759937</v>
+        <v>0.7537764350453172</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4362606232294617</v>
+        <v>0.4346666666666666</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3957597173144876</v>
+        <v>0.3831168831168831</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4496402877697842</v>
+        <v>0.4429065743944637</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3322834645669291</v>
+        <v>0.3485294117647059</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.516693163751987</v>
+        <v>1.507552870090634</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7915194346289752</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.104052573932092</v>
+        <v>1.130030959752322</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8922413793103449</v>
+        <v>0.8808080808080808</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.979539641943734</v>
+        <v>0.9878345498783455</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.747126436781609</v>
+        <v>1.736263736263736</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.331050228310502</v>
+        <v>1.326839826839827</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.86986301369863</v>
+        <v>4.893939393939394</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.200913242009133</v>
+        <v>6.220779220779221</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.39249999999998</v>
+        <v>77.25294117647057</v>
       </c>
       <c r="C3" t="n">
-        <v>77.55625000000001</v>
+        <v>77.43941176470588</v>
       </c>
       <c r="D3" t="n">
-        <v>117.5356596019018</v>
+        <v>117.5112231953634</v>
       </c>
       <c r="E3" t="n">
-        <v>119.8726730598759</v>
+        <v>120.4357106504516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5593061415846226</v>
+        <v>0.560592658115878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1527430986622773</v>
+        <v>0.1520937582301817</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3460176991150443</v>
+        <v>0.3410788381742739</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2489451476793249</v>
+        <v>0.2472357363998231</v>
       </c>
       <c r="J3" t="n">
-        <v>12.9375</v>
+        <v>12.82352941176471</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96875</v>
+        <v>11.94117647058824</v>
       </c>
       <c r="L3" t="n">
-        <v>4.75</v>
+        <v>4.647058823529412</v>
       </c>
       <c r="M3" t="n">
-        <v>12.875</v>
+        <v>12.79411764705882</v>
       </c>
       <c r="N3" t="n">
-        <v>29.8125</v>
+        <v>29.35294117647059</v>
       </c>
       <c r="O3" t="n">
-        <v>39.3125</v>
+        <v>38.94117647058823</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5897796530707923</v>
+        <v>0.5855816010614772</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8125</v>
+        <v>4.794117647058823</v>
       </c>
       <c r="R3" t="n">
-        <v>11.03125</v>
+        <v>11.02941176470588</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1654946085325832</v>
+        <v>0.1658558160106148</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.470588235294118</v>
       </c>
       <c r="U3" t="n">
-        <v>8.84375</v>
+        <v>9.058823529411764</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1326769807782466</v>
+        <v>0.1362229102167183</v>
       </c>
       <c r="W3" t="n">
-        <v>3.90625</v>
+        <v>3.764705882352941</v>
       </c>
       <c r="X3" t="n">
-        <v>8.6875</v>
+        <v>8.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1303328645100797</v>
+        <v>0.1278195488721804</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.59375</v>
+        <v>6.970588235294118</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.84375</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2977027660571964</v>
+        <v>0.3007518796992481</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7583465818759937</v>
+        <v>0.7537764350453172</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4362606232294617</v>
+        <v>0.4346666666666666</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3957597173144876</v>
+        <v>0.3831168831168831</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4496402877697842</v>
+        <v>0.4429065743944637</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3322834645669291</v>
+        <v>0.3485294117647059</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.516693163751987</v>
+        <v>1.507552870090634</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7915194346289752</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.104052573932092</v>
+        <v>1.130030959752322</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8922413793103449</v>
+        <v>0.8808080808080808</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.979539641943734</v>
+        <v>0.9878345498783455</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.747126436781609</v>
+        <v>1.736263736263737</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.331050228310502</v>
+        <v>1.326839826839827</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.86986301369863</v>
+        <v>4.893939393939394</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.200913242009133</v>
+        <v>6.220779220779221</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2487.04</v>
+        <v>2639.28</v>
       </c>
       <c r="C4" t="n">
-        <v>2481.8</v>
+        <v>2632.94</v>
       </c>
       <c r="D4" t="n">
-        <v>119.8726730598759</v>
+        <v>120.4357106504516</v>
       </c>
       <c r="E4" t="n">
-        <v>117.5356596019018</v>
+        <v>117.5112231953634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5825289575289575</v>
+        <v>0.5846572855197458</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1615014061760365</v>
+        <v>0.1620146107721714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3499546690843155</v>
+        <v>0.3558597091531223</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2707528957528957</v>
+        <v>0.2700862460281435</v>
       </c>
       <c r="J4" t="n">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="K4" t="n">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="L4" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="M4" t="n">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="N4" t="n">
-        <v>1036</v>
+        <v>1103</v>
       </c>
       <c r="O4" t="n">
-        <v>1409</v>
+        <v>1500</v>
       </c>
       <c r="P4" t="n">
-        <v>0.680019305019305</v>
+        <v>0.6808896958692692</v>
       </c>
       <c r="Q4" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="R4" t="n">
+        <v>300</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1361779391738538</v>
+      </c>
+      <c r="T4" t="n">
+        <v>89</v>
+      </c>
+      <c r="U4" t="n">
+        <v>248</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1125737630503858</v>
+      </c>
+      <c r="W4" t="n">
+        <v>117</v>
+      </c>
+      <c r="X4" t="n">
         <v>288</v>
       </c>
-      <c r="S4" t="n">
-        <v>0.138996138996139</v>
-      </c>
-      <c r="T4" t="n">
-        <v>78</v>
-      </c>
-      <c r="U4" t="n">
-        <v>226</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1090733590733591</v>
-      </c>
-      <c r="W4" t="n">
-        <v>110</v>
-      </c>
-      <c r="X4" t="n">
-        <v>272</v>
-      </c>
       <c r="Y4" t="n">
-        <v>0.1312741312741313</v>
+        <v>0.1307308216068997</v>
       </c>
       <c r="Z4" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="AA4" t="n">
-        <v>643</v>
+        <v>679</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3103281853281853</v>
+        <v>0.3082160689968225</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7352732434350603</v>
+        <v>0.7353333333333333</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4233333333333333</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3451327433628318</v>
+        <v>0.3588709677419355</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4044117647058824</v>
+        <v>0.40625</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3794712286158631</v>
+        <v>0.3814432989690721</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.470546486870121</v>
+        <v>1.470666666666667</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6902654867256637</v>
+        <v>0.717741935483871</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.160655737704918</v>
+        <v>1.166494312306101</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8835616438356164</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.018134715025907</v>
+        <v>0.9783653846153846</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.637096774193548</v>
+        <v>1.661538461538462</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.355603448275862</v>
+        <v>1.367676767676768</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.46551724137931</v>
+        <v>4.450505050505051</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.821120689655173</v>
+        <v>5.818181818181818</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.71999999999998</v>
+        <v>77.62588235294118</v>
       </c>
       <c r="C5" t="n">
-        <v>77.55625000000001</v>
+        <v>77.43941176470588</v>
       </c>
       <c r="D5" t="n">
-        <v>119.8726730598759</v>
+        <v>120.4357106504516</v>
       </c>
       <c r="E5" t="n">
-        <v>117.5356596019018</v>
+        <v>117.5112231953634</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5825289575289575</v>
+        <v>0.5846572855197457</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1615014061760365</v>
+        <v>0.1620146107721714</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3499546690843155</v>
+        <v>0.3558597091531223</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2707528957528957</v>
+        <v>0.2700862460281434</v>
       </c>
       <c r="J5" t="n">
-        <v>12.09375</v>
+        <v>12.29411764705882</v>
       </c>
       <c r="K5" t="n">
-        <v>12.28125</v>
+        <v>11.97058823529412</v>
       </c>
       <c r="L5" t="n">
-        <v>6.34375</v>
+        <v>6.352941176470588</v>
       </c>
       <c r="M5" t="n">
-        <v>13.65625</v>
+        <v>13.73529411764706</v>
       </c>
       <c r="N5" t="n">
-        <v>32.375</v>
+        <v>32.44117647058823</v>
       </c>
       <c r="O5" t="n">
-        <v>44.03125</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="P5" t="n">
-        <v>0.680019305019305</v>
+        <v>0.6808896958692692</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.84375</v>
+        <v>3.735294117647059</v>
       </c>
       <c r="R5" t="n">
-        <v>9</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="S5" t="n">
-        <v>0.138996138996139</v>
+        <v>0.1361779391738538</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4375</v>
+        <v>2.617647058823529</v>
       </c>
       <c r="U5" t="n">
-        <v>7.0625</v>
+        <v>7.294117647058823</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1090733590733591</v>
+        <v>0.1125737630503858</v>
       </c>
       <c r="W5" t="n">
-        <v>3.4375</v>
+        <v>3.441176470588236</v>
       </c>
       <c r="X5" t="n">
-        <v>8.5</v>
+        <v>8.470588235294118</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1312741312741313</v>
+        <v>0.1307308216068997</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.625</v>
+        <v>7.617647058823529</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.09375</v>
+        <v>19.97058823529412</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3103281853281853</v>
+        <v>0.3082160689968225</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7352732434350603</v>
+        <v>0.7353333333333333</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.4233333333333333</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3451327433628318</v>
+        <v>0.3588709677419355</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4044117647058824</v>
+        <v>0.40625</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3794712286158631</v>
+        <v>0.3814432989690722</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.470546486870121</v>
+        <v>1.470666666666667</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6902654867256637</v>
+        <v>0.717741935483871</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.160655737704918</v>
+        <v>1.166494312306101</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8835616438356164</v>
+        <v>0.9047619047619049</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.018134715025907</v>
+        <v>0.9783653846153847</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.637096774193548</v>
+        <v>1.661538461538461</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.355603448275862</v>
+        <v>1.367676767676768</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.46551724137931</v>
+        <v>4.450505050505051</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.821120689655173</v>
+        <v>5.818181818181818</v>
       </c>
     </row>
     <row r="7">
@@ -1419,67 +1419,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I8" t="n">
+        <v>58</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="n">
         <v>56</v>
       </c>
-      <c r="J8" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>54</v>
-      </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
+        <v>34</v>
+      </c>
+      <c r="N8" t="n">
         <v>31</v>
       </c>
-      <c r="N8" t="n">
-        <v>29</v>
-      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="S8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T8" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="U8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="V8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="W8" t="n">
         <v>23</v>
@@ -1488,22 +1488,22 @@
         <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Z8" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="AB8" t="n">
         <v>10</v>
       </c>
       <c r="AC8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1518,57 +1518,57 @@
         <v>12</v>
       </c>
       <c r="AI8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.343</v>
+        <v>0.324</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.192</v>
+        <v>0.233</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>501:36</t>
+          <t>537:29</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>192.64</v>
+        <v>203.52</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.52</v>
+        <v>0.515</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.569</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.049</v>
+        <v>1.042</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.078</v>
+        <v>0.079</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.281</v>
+        <v>0.278</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.133</v>
+        <v>1.188</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.125</v>
+        <v>0.121</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="9">
@@ -1724,10 +1724,10 @@
         <v>0.029</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="10">
@@ -1737,67 +1737,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
         <v>3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1827,10 +1827,10 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1842,51 +1842,51 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AM10" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>40:19</t>
+        </is>
+      </c>
+      <c r="AO10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AS10" t="n">
         <v>0.25</v>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19:46</t>
-        </is>
-      </c>
-      <c r="AO10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.308</v>
-      </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.294</v>
+        <v>0.222</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="11">
@@ -1896,37 +1896,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I11" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J11" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M11" t="n">
         <v>28</v>
@@ -1938,25 +1938,25 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="Q11" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="R11" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="S11" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="T11" t="n">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="U11" t="n">
         <v>39</v>
       </c>
       <c r="V11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="W11" t="n">
         <v>12</v>
@@ -1965,31 +1965,31 @@
         <v>6</v>
       </c>
       <c r="Y11" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Z11" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.66</v>
+        <v>0.632</v>
       </c>
       <c r="AB11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC11" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.344</v>
+        <v>0.358</v>
       </c>
       <c r="AE11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AF11" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.441</v>
+        <v>0.455</v>
       </c>
       <c r="AH11" t="n">
         <v>2</v>
@@ -2001,51 +2001,51 @@
         <v>0.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.313</v>
+        <v>0.347</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>605:21</t>
+          <t>645:48</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>339.24</v>
+        <v>368.56</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.457</v>
+        <v>0.469</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.487</v>
+        <v>0.496</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.79</v>
+        <v>0.806</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.189</v>
+        <v>0.187</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.137</v>
+        <v>0.129</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.359</v>
+        <v>2.319</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.25</v>
+        <v>0.256</v>
       </c>
       <c r="AW11" t="n">
         <v>0.019</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.164</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="12">
@@ -2055,16 +2055,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2073,49 +2073,49 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="S12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="T12" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="U12" t="n">
         <v>17</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="W12" t="n">
         <v>5</v>
@@ -2124,31 +2124,31 @@
         <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="Z12" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.651</v>
+        <v>0.638</v>
       </c>
       <c r="AB12" t="n">
         <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2170,41 +2170,41 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>319:39</t>
+          <t>350:40</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>130.44</v>
+        <v>140.52</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.614</v>
+        <v>0.617</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.616</v>
+        <v>0.611</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.043</v>
+        <v>1.039</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.153</v>
+        <v>0.149</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.7</v>
+        <v>0.714</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.082</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.138</v>
+        <v>0.129</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="13">
@@ -2214,153 +2214,153 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>34</v>
+      </c>
+      <c r="C13" t="n">
+        <v>498</v>
+      </c>
+      <c r="D13" t="n">
+        <v>66</v>
+      </c>
+      <c r="E13" t="n">
+        <v>136</v>
+      </c>
+      <c r="F13" t="n">
+        <v>76</v>
+      </c>
+      <c r="G13" t="n">
+        <v>179</v>
+      </c>
+      <c r="H13" t="n">
+        <v>138</v>
+      </c>
+      <c r="I13" t="n">
+        <v>154</v>
+      </c>
+      <c r="J13" t="n">
+        <v>48</v>
+      </c>
+      <c r="K13" t="n">
+        <v>50</v>
+      </c>
+      <c r="L13" t="n">
+        <v>19</v>
+      </c>
+      <c r="M13" t="n">
+        <v>24</v>
+      </c>
+      <c r="N13" t="n">
+        <v>19</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>50</v>
+      </c>
+      <c r="R13" t="n">
+        <v>63</v>
+      </c>
+      <c r="S13" t="n">
+        <v>151</v>
+      </c>
+      <c r="T13" t="n">
+        <v>507</v>
+      </c>
+      <c r="U13" t="n">
+        <v>83</v>
+      </c>
+      <c r="V13" t="n">
         <v>32</v>
       </c>
-      <c r="C13" t="n">
-        <v>447</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62</v>
-      </c>
-      <c r="E13" t="n">
-        <v>121</v>
-      </c>
-      <c r="F13" t="n">
-        <v>66</v>
-      </c>
-      <c r="G13" t="n">
-        <v>164</v>
-      </c>
-      <c r="H13" t="n">
-        <v>125</v>
-      </c>
-      <c r="I13" t="n">
-        <v>139</v>
-      </c>
-      <c r="J13" t="n">
-        <v>46</v>
-      </c>
-      <c r="K13" t="n">
-        <v>47</v>
-      </c>
-      <c r="L13" t="n">
-        <v>17</v>
-      </c>
-      <c r="M13" t="n">
-        <v>21</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="W13" t="n">
+        <v>30</v>
+      </c>
+      <c r="X13" t="n">
         <v>18</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>47</v>
-      </c>
-      <c r="R13" t="n">
-        <v>59</v>
-      </c>
-      <c r="S13" t="n">
-        <v>137</v>
-      </c>
-      <c r="T13" t="n">
-        <v>456</v>
-      </c>
-      <c r="U13" t="n">
-        <v>71</v>
-      </c>
-      <c r="V13" t="n">
-        <v>25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>28</v>
-      </c>
-      <c r="X13" t="n">
-        <v>16</v>
-      </c>
       <c r="Y13" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="Z13" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.826</v>
+        <v>0.824</v>
       </c>
       <c r="AB13" t="n">
         <v>17</v>
       </c>
       <c r="AC13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF13" t="n">
         <v>38</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>32</v>
-      </c>
       <c r="AG13" t="n">
-        <v>0.406</v>
+        <v>0.368</v>
       </c>
       <c r="AH13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="AL13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.405</v>
+        <v>0.432</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>702:40</t>
+          <t>757:08</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>393.16</v>
+        <v>432.76</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.646</v>
+        <v>0.651</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.137</v>
+        <v>1.151</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.12</v>
+        <v>0.116</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.979</v>
+        <v>0.96</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.25</v>
+        <v>0.256</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="AY13" t="n">
         <v>0.051</v>
@@ -2373,40 +2373,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="D14" t="n">
         <v>43</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I14" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N14" t="n">
         <v>7</v>
@@ -2415,22 +2415,22 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R14" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T14" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="U14" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="V14" t="n">
         <v>25</v>
@@ -2442,13 +2442,13 @@
         <v>8</v>
       </c>
       <c r="Y14" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Z14" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="AB14" t="n">
         <v>7</v>
@@ -2463,66 +2463,66 @@
         <v>17</v>
       </c>
       <c r="AF14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.415</v>
+        <v>0.386</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.255</v>
+        <v>0.267</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>673:53</t>
+          <t>726:30</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>217.28</v>
+        <v>231.92</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.532</v>
+        <v>0.526</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.054</v>
+        <v>1.043</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.173</v>
+        <v>0.184</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.812</v>
+        <v>1.765</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.191</v>
+        <v>0.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
@@ -2675,13 +2675,13 @@
         <v>0.143</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="16">
@@ -2691,100 +2691,100 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H16" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="K16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M16" t="n">
         <v>27</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q16" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="R16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="S16" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="T16" t="n">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="U16" t="n">
         <v>24</v>
       </c>
       <c r="V16" t="n">
+        <v>35</v>
+      </c>
+      <c r="W16" t="n">
+        <v>10</v>
+      </c>
+      <c r="X16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>84</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>119</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AB16" t="n">
         <v>33</v>
       </c>
-      <c r="W16" t="n">
-        <v>8</v>
-      </c>
-      <c r="X16" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>77</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>30</v>
-      </c>
       <c r="AC16" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.492</v>
+        <v>0.5</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.483</v>
+        <v>0.438</v>
       </c>
       <c r="AH16" t="n">
         <v>7</v>
@@ -2796,48 +2796,48 @@
         <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.259</v>
+        <v>0.267</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>595:32</t>
+          <t>636:24</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>331.16</v>
+        <v>353.8</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.513</v>
+        <v>0.512</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.551</v>
+        <v>0.552</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.839</v>
+        <v>0.845</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.239</v>
+        <v>0.235</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.214</v>
+        <v>0.221</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.139</v>
+        <v>2.157</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.248</v>
+        <v>0.249</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="AY16" t="n">
         <v>0.183</v>
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="D17" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E17" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H17" t="n">
         <v>53</v>
@@ -2877,34 +2877,34 @@
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R17" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="S17" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T17" t="n">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="U17" t="n">
         <v>30</v>
@@ -2913,37 +2913,37 @@
         <v>77</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="Z17" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.469</v>
+        <v>0.486</v>
       </c>
       <c r="AE17" t="n">
         <v>12</v>
       </c>
       <c r="AF17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.462</v>
+        <v>0.429</v>
       </c>
       <c r="AH17" t="n">
         <v>1</v>
@@ -2955,51 +2955,51 @@
         <v>0.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.316</v>
+        <v>0.366</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>534:27</t>
+          <t>576:45</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>291.48</v>
+        <v>306.48</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.676</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.702</v>
+        <v>0.711</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.235</v>
+        <v>1.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.233</v>
+        <v>0.221</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.429</v>
+        <v>0.405</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.243</v>
+        <v>0.238</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.134</v>
+        <v>0.125</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.213</v>
+        <v>0.204</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="18">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
         <v>29</v>
@@ -3149,16 +3149,16 @@
         <v>2.625</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.208</v>
+        <v>0.209</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.089</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19">
@@ -3327,22 +3327,22 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="C20" t="n">
+      <c r="G20" t="n">
         <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U20" t="n">
         <v>3</v>
@@ -3432,33 +3432,33 @@
         <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AO20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP20" t="n">
         <v>1</v>
       </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>03:43</t>
-        </is>
-      </c>
-      <c r="AO20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.36</v>
+        <v>0.148</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.305</v>
+        <v>0.093</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -3486,61 +3486,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L21" t="n">
         <v>25</v>
       </c>
       <c r="M21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R21" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="S21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T21" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="U21" t="n">
         <v>44</v>
@@ -3555,87 +3555,87 @@
         <v>8</v>
       </c>
       <c r="Y21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.55</v>
+        <v>0.571</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.421</v>
+        <v>0.4</v>
       </c>
       <c r="AH21" t="n">
         <v>29</v>
       </c>
       <c r="AI21" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.537</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AL21" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.462</v>
+        <v>0.449</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>638:45</t>
+          <t>680:30</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>217.28</v>
+        <v>228.16</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.675</v>
+        <v>0.659</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.699</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.224</v>
+        <v>1.192</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.407</v>
+        <v>1.379</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.152</v>
+        <v>0.15</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.044</v>
+        <v>0.041</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="22">
@@ -3645,22 +3645,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H22" t="n">
         <v>13</v>
@@ -3672,7 +3672,7 @@
         <v>32</v>
       </c>
       <c r="K22" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L22" t="n">
         <v>19</v>
@@ -3687,22 +3687,22 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R22" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="S22" t="n">
         <v>33</v>
       </c>
       <c r="T22" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="U22" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="V22" t="n">
         <v>23</v>
@@ -3714,22 +3714,22 @@
         <v>7</v>
       </c>
       <c r="Y22" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.646</v>
+        <v>0.64</v>
       </c>
       <c r="AB22" t="n">
         <v>6</v>
       </c>
       <c r="AC22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -3741,13 +3741,13 @@
         <v>0.167</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.354</v>
+        <v>0.36</v>
       </c>
       <c r="AK22" t="n">
         <v>26</v>
@@ -3760,41 +3760,41 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>665:23</t>
+          <t>698:31</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>229.12</v>
+        <v>237.12</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.478</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.855</v>
+        <v>0.848</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.105</v>
+        <v>0.114</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.333</v>
+        <v>1.185</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.154</v>
+        <v>0.152</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="AX22" t="n">
         <v>0.08</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="23">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -3831,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L23" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3846,13 +3846,13 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -3963,153 +3963,153 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
-        <v>2917</v>
+        <v>3094</v>
       </c>
       <c r="D24" t="n">
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="E24" t="n">
-        <v>1220</v>
+        <v>1292</v>
       </c>
       <c r="F24" t="n">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="G24" t="n">
-        <v>913</v>
+        <v>969</v>
       </c>
       <c r="H24" t="n">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="I24" t="n">
-        <v>674</v>
+        <v>715</v>
       </c>
       <c r="J24" t="n">
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="K24" t="n">
-        <v>717</v>
+        <v>753</v>
       </c>
       <c r="L24" t="n">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="M24" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="N24" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="Q24" t="n">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="R24" t="n">
-        <v>756</v>
+        <v>804</v>
       </c>
       <c r="S24" t="n">
-        <v>707</v>
+        <v>752</v>
       </c>
       <c r="T24" t="n">
-        <v>3288</v>
+        <v>3469</v>
       </c>
       <c r="U24" t="n">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="V24" t="n">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="W24" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="X24" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="Y24" t="n">
-        <v>954</v>
+        <v>998</v>
       </c>
       <c r="Z24" t="n">
-        <v>1258</v>
+        <v>1324</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="AB24" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="AC24" t="n">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="AE24" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="AF24" t="n">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.396</v>
+        <v>0.383</v>
       </c>
       <c r="AH24" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AI24" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.45</v>
+        <v>0.443</v>
       </c>
       <c r="AK24" t="n">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="n">
-        <v>635</v>
+        <v>680</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.332</v>
+        <v>0.349</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6800:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>2867.56</v>
+        <v>3037.6</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.6</v>
+        <v>0.601</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.017</v>
+        <v>1.019</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.249</v>
+        <v>0.247</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.331</v>
+        <v>1.327</v>
       </c>
       <c r="AV24" t="n">
         <v>0.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -4122,153 +4122,153 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="n">
-        <v>2975</v>
+        <v>3171</v>
       </c>
       <c r="D25" t="n">
-        <v>676</v>
+        <v>724</v>
       </c>
       <c r="E25" t="n">
-        <v>1157</v>
+        <v>1236</v>
       </c>
       <c r="F25" t="n">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="G25" t="n">
-        <v>915</v>
+        <v>967</v>
       </c>
       <c r="H25" t="n">
-        <v>561</v>
+        <v>595</v>
       </c>
       <c r="I25" t="n">
-        <v>766</v>
+        <v>812</v>
       </c>
       <c r="J25" t="n">
-        <v>629</v>
+        <v>677</v>
       </c>
       <c r="K25" t="n">
-        <v>739</v>
+        <v>794</v>
       </c>
       <c r="L25" t="n">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="M25" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="N25" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="Q25" t="n">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="R25" t="n">
-        <v>713</v>
+        <v>757</v>
       </c>
       <c r="S25" t="n">
-        <v>745</v>
+        <v>793</v>
       </c>
       <c r="T25" t="n">
-        <v>3478</v>
+        <v>3730</v>
       </c>
       <c r="U25" t="n">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="V25" t="n">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="W25" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="X25" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="Y25" t="n">
-        <v>1036</v>
+        <v>1103</v>
       </c>
       <c r="Z25" t="n">
-        <v>1409</v>
+        <v>1500</v>
       </c>
       <c r="AA25" t="n">
         <v>0.735</v>
       </c>
       <c r="AB25" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AC25" t="n">
+        <v>300</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>89</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>248</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>117</v>
+      </c>
+      <c r="AI25" t="n">
         <v>288</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>78</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>226</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>272</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>0.404</v>
+        <v>0.406</v>
       </c>
       <c r="AK25" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="n">
-        <v>643</v>
+        <v>679</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6800:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>2873.04</v>
+        <v>3055.28</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.583</v>
+        <v>0.585</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.617</v>
+        <v>0.619</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.035</v>
+        <v>1.038</v>
       </c>
       <c r="AS25" t="n">
         <v>0.162</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.356</v>
+        <v>1.368</v>
       </c>
       <c r="AV25" t="n">
         <v>0.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -4338,43 +4338,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>6.733</v>
+        <v>6.625</v>
       </c>
       <c r="D27" t="n">
-        <v>1.8</v>
+        <v>1.719</v>
       </c>
       <c r="E27" t="n">
-        <v>3.067</v>
+        <v>2.969</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.594</v>
       </c>
       <c r="G27" t="n">
-        <v>2.033</v>
+        <v>2.094</v>
       </c>
       <c r="H27" t="n">
-        <v>1.433</v>
+        <v>1.406</v>
       </c>
       <c r="I27" t="n">
-        <v>1.867</v>
+        <v>1.812</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.594</v>
       </c>
       <c r="K27" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.667</v>
+        <v>1.656</v>
       </c>
       <c r="M27" t="n">
-        <v>1.033</v>
+        <v>1.062</v>
       </c>
       <c r="N27" t="n">
-        <v>0.967</v>
+        <v>0.969</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4386,108 +4386,108 @@
         <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.367</v>
+        <v>2.344</v>
       </c>
       <c r="S27" t="n">
-        <v>1.467</v>
+        <v>1.406</v>
       </c>
       <c r="T27" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="U27" t="n">
-        <v>1.167</v>
+        <v>1.156</v>
       </c>
       <c r="V27" t="n">
-        <v>1.567</v>
+        <v>1.531</v>
       </c>
       <c r="W27" t="n">
-        <v>0.767</v>
+        <v>0.719</v>
       </c>
       <c r="X27" t="n">
-        <v>0.433</v>
+        <v>0.406</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.9</v>
+        <v>2.812</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.967</v>
+        <v>3.844</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.767</v>
+        <v>0.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.167</v>
+        <v>1.156</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.343</v>
+        <v>0.324</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.167</v>
+        <v>0.219</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.867</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.192</v>
+        <v>0.233</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>6.421</v>
+        <v>6.36</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.52</v>
+        <v>0.515</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.569</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.049</v>
+        <v>1.042</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.078</v>
+        <v>0.079</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.281</v>
+        <v>0.278</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.133</v>
+        <v>1.188</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.125</v>
+        <v>0.121</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="28">
@@ -4643,7 +4643,7 @@
         <v>0.029</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="AY28" t="n">
         <v>0.037</v>
@@ -4656,19 +4656,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G29" t="n">
         <v>2.5</v>
@@ -4680,16 +4680,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>0.5</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N29" t="n">
         <v>0.5</v>
@@ -4698,25 +4698,25 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -4728,84 +4728,84 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AD29" t="n">
         <v>1</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AM29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AS29" t="n">
         <v>0.25</v>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.308</v>
-      </c>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.294</v>
+        <v>0.222</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.016</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="30">
@@ -4815,153 +4815,153 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C30" t="n">
-        <v>9.241</v>
+        <v>9.581</v>
       </c>
       <c r="D30" t="n">
-        <v>2.828</v>
+        <v>2.903</v>
       </c>
       <c r="E30" t="n">
-        <v>6.207</v>
+        <v>6.387</v>
       </c>
       <c r="F30" t="n">
-        <v>0.793</v>
+        <v>0.871</v>
       </c>
       <c r="G30" t="n">
-        <v>2.586</v>
+        <v>2.581</v>
       </c>
       <c r="H30" t="n">
-        <v>1.207</v>
+        <v>1.161</v>
       </c>
       <c r="I30" t="n">
-        <v>1.586</v>
+        <v>1.581</v>
       </c>
       <c r="J30" t="n">
-        <v>5.207</v>
+        <v>5.161</v>
       </c>
       <c r="K30" t="n">
-        <v>0.931</v>
+        <v>0.968</v>
       </c>
       <c r="L30" t="n">
-        <v>0.345</v>
+        <v>0.355</v>
       </c>
       <c r="M30" t="n">
-        <v>0.966</v>
+        <v>0.903</v>
       </c>
       <c r="N30" t="n">
-        <v>0.414</v>
+        <v>0.387</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.207</v>
+        <v>2.226</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.207</v>
+        <v>2.226</v>
       </c>
       <c r="R30" t="n">
-        <v>2.517</v>
+        <v>2.484</v>
       </c>
       <c r="S30" t="n">
-        <v>2.414</v>
+        <v>2.452</v>
       </c>
       <c r="T30" t="n">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="U30" t="n">
-        <v>1.345</v>
+        <v>1.258</v>
       </c>
       <c r="V30" t="n">
-        <v>0.931</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="W30" t="n">
-        <v>0.414</v>
+        <v>0.387</v>
       </c>
       <c r="X30" t="n">
-        <v>0.207</v>
+        <v>0.194</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.414</v>
+        <v>2.323</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.655</v>
+        <v>3.677</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.66</v>
+        <v>0.632</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.724</v>
+        <v>0.774</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.103</v>
+        <v>2.161</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.344</v>
+        <v>0.358</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.897</v>
+        <v>0.968</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.034</v>
+        <v>2.129</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.441</v>
+        <v>0.455</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.276</v>
+        <v>0.258</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.724</v>
+        <v>0.806</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.31</v>
+        <v>2.323</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.313</v>
+        <v>0.347</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>11.698</v>
+        <v>11.889</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.457</v>
+        <v>0.469</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.487</v>
+        <v>0.496</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.79</v>
+        <v>0.806</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.189</v>
+        <v>0.187</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.137</v>
+        <v>0.129</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.359</v>
+        <v>2.319</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.25</v>
+        <v>0.256</v>
       </c>
       <c r="AW30" t="n">
         <v>0.019</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="AY30" t="n">
         <v>0.183</v>
@@ -4974,100 +4974,100 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>4.25</v>
+        <v>4.294</v>
       </c>
       <c r="D31" t="n">
-        <v>1.688</v>
+        <v>1.706</v>
       </c>
       <c r="E31" t="n">
-        <v>2.719</v>
+        <v>2.735</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="H31" t="n">
-        <v>0.875</v>
+        <v>0.882</v>
       </c>
       <c r="I31" t="n">
-        <v>1.594</v>
+        <v>1.706</v>
       </c>
       <c r="J31" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="K31" t="n">
-        <v>1.188</v>
+        <v>1.147</v>
       </c>
       <c r="L31" t="n">
-        <v>0.719</v>
+        <v>0.794</v>
       </c>
       <c r="M31" t="n">
-        <v>0.219</v>
+        <v>0.265</v>
       </c>
       <c r="N31" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="R31" t="n">
-        <v>1.969</v>
+        <v>2.029</v>
       </c>
       <c r="S31" t="n">
-        <v>1.469</v>
+        <v>1.529</v>
       </c>
       <c r="T31" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="U31" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0.406</v>
+        <v>0.588</v>
       </c>
       <c r="W31" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="X31" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.156</v>
+        <v>2.176</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.312</v>
+        <v>3.412</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.651</v>
+        <v>0.638</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.781</v>
+        <v>0.765</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.062</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.219</v>
+        <v>0.265</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5082,48 +5082,48 @@
         <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AM31" t="n">
         <v>0</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>4.076</v>
+        <v>4.133</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.614</v>
+        <v>0.617</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.616</v>
+        <v>0.611</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.043</v>
+        <v>1.039</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.153</v>
+        <v>0.149</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.7</v>
+        <v>0.714</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.182</v>
+        <v>0.179</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.082</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.138</v>
+        <v>0.129</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="32">
@@ -5133,153 +5133,153 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>13.969</v>
+        <v>14.647</v>
       </c>
       <c r="D32" t="n">
-        <v>1.938</v>
+        <v>1.941</v>
       </c>
       <c r="E32" t="n">
-        <v>3.781</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>2.062</v>
+        <v>2.235</v>
       </c>
       <c r="G32" t="n">
-        <v>5.125</v>
+        <v>5.265</v>
       </c>
       <c r="H32" t="n">
-        <v>3.906</v>
+        <v>4.059</v>
       </c>
       <c r="I32" t="n">
-        <v>4.344</v>
+        <v>4.529</v>
       </c>
       <c r="J32" t="n">
-        <v>1.438</v>
+        <v>1.412</v>
       </c>
       <c r="K32" t="n">
-        <v>1.469</v>
+        <v>1.471</v>
       </c>
       <c r="L32" t="n">
-        <v>0.531</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>0.656</v>
+        <v>0.706</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.469</v>
+        <v>1.471</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.469</v>
+        <v>1.471</v>
       </c>
       <c r="R32" t="n">
-        <v>1.844</v>
+        <v>1.853</v>
       </c>
       <c r="S32" t="n">
-        <v>4.281</v>
+        <v>4.441</v>
       </c>
       <c r="T32" t="n">
-        <v>456</v>
+        <v>507</v>
       </c>
       <c r="U32" t="n">
-        <v>2.219</v>
+        <v>2.441</v>
       </c>
       <c r="V32" t="n">
-        <v>0.781</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>0.875</v>
+        <v>0.882</v>
       </c>
       <c r="X32" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>5.088</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="AB32" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y32" t="n">
-        <v>4.906</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5.938</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.531</v>
-      </c>
       <c r="AC32" t="n">
-        <v>1.188</v>
+        <v>1.235</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.447</v>
+        <v>0.405</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>1.118</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.406</v>
+        <v>0.368</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.188</v>
+        <v>1.176</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.594</v>
+        <v>1.765</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.938</v>
+        <v>4.088</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.405</v>
+        <v>0.432</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>12.286</v>
+        <v>12.728</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.646</v>
+        <v>0.651</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.137</v>
+        <v>1.151</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.12</v>
+        <v>0.116</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.979</v>
+        <v>0.96</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.25</v>
+        <v>0.256</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="AY32" t="n">
         <v>0.051</v>
@@ -5292,43 +5292,43 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>7.156</v>
+        <v>7.118</v>
       </c>
       <c r="D33" t="n">
-        <v>1.344</v>
+        <v>1.265</v>
       </c>
       <c r="E33" t="n">
-        <v>2.656</v>
+        <v>2.588</v>
       </c>
       <c r="F33" t="n">
-        <v>1.156</v>
+        <v>1.176</v>
       </c>
       <c r="G33" t="n">
-        <v>3.125</v>
+        <v>3.176</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="I33" t="n">
-        <v>1.156</v>
+        <v>1.265</v>
       </c>
       <c r="J33" t="n">
-        <v>0.906</v>
+        <v>0.882</v>
       </c>
       <c r="K33" t="n">
-        <v>3.469</v>
+        <v>3.676</v>
       </c>
       <c r="L33" t="n">
-        <v>1.094</v>
+        <v>1.147</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="N33" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5340,108 +5340,108 @@
         <v>0.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.031</v>
+        <v>2.088</v>
       </c>
       <c r="S33" t="n">
-        <v>0.9379999999999999</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="U33" t="n">
-        <v>1.469</v>
+        <v>1.529</v>
       </c>
       <c r="V33" t="n">
-        <v>0.781</v>
+        <v>0.735</v>
       </c>
       <c r="W33" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="X33" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.594</v>
+        <v>1.618</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.969</v>
+        <v>2.029</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="AD33" t="n">
         <v>0.389</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.281</v>
+        <v>1.294</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.415</v>
+        <v>0.386</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.406</v>
+        <v>1.412</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.438</v>
+        <v>0.471</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.719</v>
+        <v>1.765</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.255</v>
+        <v>0.267</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.79</v>
+        <v>6.821</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.532</v>
+        <v>0.526</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.054</v>
+        <v>1.043</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.173</v>
+        <v>0.184</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.812</v>
+        <v>1.765</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.191</v>
+        <v>0.2</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34">
@@ -5594,13 +5594,13 @@
         <v>0.143</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="35">
@@ -5610,153 +5610,153 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>8.688000000000001</v>
+        <v>8.794</v>
       </c>
       <c r="D35" t="n">
-        <v>2.281</v>
+        <v>2.294</v>
       </c>
       <c r="E35" t="n">
-        <v>4.25</v>
+        <v>4.324</v>
       </c>
       <c r="F35" t="n">
-        <v>0.875</v>
+        <v>0.882</v>
       </c>
       <c r="G35" t="n">
-        <v>2.75</v>
+        <v>2.735</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5</v>
+        <v>1.559</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>2.059</v>
       </c>
       <c r="J35" t="n">
-        <v>5.281</v>
+        <v>5.265</v>
       </c>
       <c r="K35" t="n">
-        <v>1.312</v>
+        <v>1.294</v>
       </c>
       <c r="L35" t="n">
-        <v>0.75</v>
+        <v>0.735</v>
       </c>
       <c r="M35" t="n">
-        <v>0.844</v>
+        <v>0.794</v>
       </c>
       <c r="N35" t="n">
-        <v>0.219</v>
+        <v>0.235</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.469</v>
+        <v>2.441</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.469</v>
+        <v>2.441</v>
       </c>
       <c r="R35" t="n">
-        <v>1.438</v>
+        <v>1.441</v>
       </c>
       <c r="S35" t="n">
-        <v>2.125</v>
+        <v>2.353</v>
       </c>
       <c r="T35" t="n">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="U35" t="n">
-        <v>0.75</v>
+        <v>0.706</v>
       </c>
       <c r="V35" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="W35" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="X35" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.406</v>
+        <v>2.471</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.438</v>
+        <v>3.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.7</v>
+        <v>0.706</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.971</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.906</v>
+        <v>1.941</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.492</v>
+        <v>0.5</v>
       </c>
       <c r="AE35" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.438</v>
       </c>
-      <c r="AF35" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.483</v>
-      </c>
       <c r="AH35" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AJ35" t="n">
         <v>1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.656</v>
+        <v>0.676</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.531</v>
+        <v>2.529</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.259</v>
+        <v>0.267</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>10.349</v>
+        <v>10.406</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.513</v>
+        <v>0.512</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.551</v>
+        <v>0.552</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.839</v>
+        <v>0.845</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.239</v>
+        <v>0.235</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.214</v>
+        <v>0.221</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.139</v>
+        <v>2.157</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.248</v>
+        <v>0.249</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="AY35" t="n">
         <v>0.183</v>
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>11.25</v>
+        <v>11.265</v>
       </c>
       <c r="D36" t="n">
-        <v>4.188</v>
+        <v>4.147</v>
       </c>
       <c r="E36" t="n">
-        <v>5.844</v>
+        <v>5.794</v>
       </c>
       <c r="F36" t="n">
-        <v>0.406</v>
+        <v>0.471</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25</v>
+        <v>1.265</v>
       </c>
       <c r="H36" t="n">
-        <v>1.656</v>
+        <v>1.559</v>
       </c>
       <c r="I36" t="n">
-        <v>2.094</v>
+        <v>1.971</v>
       </c>
       <c r="J36" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="K36" t="n">
-        <v>3.062</v>
+        <v>2.971</v>
       </c>
       <c r="L36" t="n">
-        <v>1.969</v>
+        <v>1.882</v>
       </c>
       <c r="M36" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="N36" t="n">
-        <v>1.469</v>
+        <v>1.471</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.094</v>
+        <v>1.088</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.094</v>
+        <v>1.088</v>
       </c>
       <c r="R36" t="n">
-        <v>2.562</v>
+        <v>2.647</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>1.912</v>
       </c>
       <c r="T36" t="n">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="U36" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="V36" t="n">
-        <v>2.406</v>
+        <v>2.265</v>
       </c>
       <c r="W36" t="n">
-        <v>0.188</v>
+        <v>0.235</v>
       </c>
       <c r="X36" t="n">
-        <v>0.094</v>
+        <v>0.118</v>
       </c>
       <c r="Y36" t="n">
-        <v>5</v>
+        <v>4.853</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.125</v>
+        <v>5.912</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.469</v>
+        <v>0.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>1.029</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.469</v>
+        <v>0.486</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.462</v>
+        <v>0.429</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.375</v>
+        <v>0.441</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.188</v>
+        <v>1.206</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.316</v>
+        <v>0.366</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>9.109</v>
+        <v>9.013999999999999</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.676</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.702</v>
+        <v>0.711</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.235</v>
+        <v>1.25</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.233</v>
+        <v>0.221</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.429</v>
+        <v>0.405</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.243</v>
+        <v>0.238</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.134</v>
+        <v>0.125</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.213</v>
+        <v>0.204</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="37">
@@ -5928,126 +5928,126 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="D37" t="n">
-        <v>0.323</v>
+        <v>0.303</v>
       </c>
       <c r="E37" t="n">
-        <v>0.548</v>
+        <v>0.515</v>
       </c>
       <c r="F37" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="G37" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="H37" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="I37" t="n">
-        <v>0.355</v>
+        <v>0.333</v>
       </c>
       <c r="J37" t="n">
-        <v>0.677</v>
+        <v>0.636</v>
       </c>
       <c r="K37" t="n">
-        <v>0.323</v>
+        <v>0.303</v>
       </c>
       <c r="L37" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="M37" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="N37" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="R37" t="n">
-        <v>0.452</v>
+        <v>0.424</v>
       </c>
       <c r="S37" t="n">
-        <v>0.419</v>
+        <v>0.394</v>
       </c>
       <c r="T37" t="n">
         <v>43</v>
       </c>
       <c r="U37" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="V37" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="W37" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="X37" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.226</v>
+        <v>0.212</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.452</v>
+        <v>0.424</v>
       </c>
       <c r="AA37" t="n">
         <v>0.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="AD37" t="n">
         <v>0.375</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="AG37" t="n">
         <v>0.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.333</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="AM37" t="n">
         <v>0.333</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>02:28</t>
+          <t>02:19</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>1.156</v>
+        <v>1.086</v>
       </c>
       <c r="AP37" t="n">
         <v>0.5649999999999999</v>
@@ -6068,16 +6068,16 @@
         <v>2.625</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.208</v>
+        <v>0.209</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.089</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="38">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
         <v>1.5</v>
@@ -6261,7 +6261,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -6276,34 +6276,34 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R39" t="n">
         <v>0.5</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
       <c r="S39" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U39" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6342,42 +6342,42 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AJ39" t="n">
         <v>1</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AL39" t="n">
         <v>0.5</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>01:51</t>
+          <t>03:01</t>
         </is>
       </c>
       <c r="AO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="n">
         <v>1.5</v>
       </c>
-      <c r="AP39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1</v>
-      </c>
       <c r="AS39" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AT39" t="n">
         <v>0</v>
@@ -6386,10 +6386,10 @@
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.36</v>
+        <v>0.148</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.305</v>
+        <v>0.093</v>
       </c>
       <c r="AX39" t="n">
         <v>0</v>
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C40" t="n">
-        <v>9.172000000000001</v>
+        <v>8.773999999999999</v>
       </c>
       <c r="D40" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.903</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.161</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="T40" t="n">
+        <v>268</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="AK40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="n">
-        <v>1.966</v>
-      </c>
-      <c r="F40" t="n">
-        <v>2.034</v>
-      </c>
-      <c r="G40" t="n">
-        <v>4.034</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1.069</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1.276</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.862</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.931</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.931</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2.138</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.655</v>
-      </c>
-      <c r="T40" t="n">
-        <v>264</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.517</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.207</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.414</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.897</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.793</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.034</v>
-      </c>
       <c r="AL40" t="n">
-        <v>2.241</v>
+        <v>2.226</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.462</v>
+        <v>0.449</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>7.492</v>
+        <v>7.36</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.675</v>
+        <v>0.659</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.699</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.224</v>
+        <v>1.192</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.407</v>
+        <v>1.379</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.152</v>
+        <v>0.15</v>
       </c>
       <c r="AW40" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AY40" t="n">
         <v>0.044</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0.045</v>
       </c>
     </row>
     <row r="41">
@@ -6564,156 +6564,156 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C41" t="n">
-        <v>6.125</v>
+        <v>5.912</v>
       </c>
       <c r="D41" t="n">
-        <v>0.844</v>
+        <v>0.824</v>
       </c>
       <c r="E41" t="n">
-        <v>1.781</v>
+        <v>1.765</v>
       </c>
       <c r="F41" t="n">
-        <v>1.344</v>
+        <v>1.294</v>
       </c>
       <c r="G41" t="n">
-        <v>4.312</v>
+        <v>4.118</v>
       </c>
       <c r="H41" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="I41" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>1.438</v>
+        <v>1.412</v>
       </c>
       <c r="L41" t="n">
-        <v>0.594</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="N41" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.75</v>
+        <v>0.794</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.75</v>
+        <v>0.794</v>
       </c>
       <c r="R41" t="n">
-        <v>2.031</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.031</v>
+        <v>0.971</v>
       </c>
       <c r="T41" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="U41" t="n">
-        <v>1.156</v>
+        <v>1.176</v>
       </c>
       <c r="V41" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="W41" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="X41" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.969</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.5</v>
+        <v>1.471</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.646</v>
+        <v>0.64</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="AG41" t="n">
         <v>0.167</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.5</v>
+        <v>1.471</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.354</v>
+        <v>0.36</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.812</v>
+        <v>2.647</v>
       </c>
       <c r="AM41" t="n">
         <v>0.289</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>7.16</v>
+        <v>6.974</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.478</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.855</v>
+        <v>0.848</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.105</v>
+        <v>0.114</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.333</v>
+        <v>1.185</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.154</v>
+        <v>0.152</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="AX41" t="n">
         <v>0.08</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="42">
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -6750,10 +6750,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1.812</v>
+        <v>1.765</v>
       </c>
       <c r="L42" t="n">
-        <v>1.688</v>
+        <v>1.647</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -6765,13 +6765,13 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.219</v>
+        <v>0.235</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -6882,118 +6882,118 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C43" t="n">
-        <v>91.15600000000001</v>
+        <v>91</v>
       </c>
       <c r="D43" t="n">
-        <v>21.531</v>
+        <v>21.176</v>
       </c>
       <c r="E43" t="n">
-        <v>38.125</v>
+        <v>38</v>
       </c>
       <c r="F43" t="n">
-        <v>10.5</v>
+        <v>10.735</v>
       </c>
       <c r="G43" t="n">
-        <v>28.531</v>
+        <v>28.5</v>
       </c>
       <c r="H43" t="n">
-        <v>16.594</v>
+        <v>16.441</v>
       </c>
       <c r="I43" t="n">
-        <v>21.062</v>
+        <v>21.029</v>
       </c>
       <c r="J43" t="n">
-        <v>18.219</v>
+        <v>18.029</v>
       </c>
       <c r="K43" t="n">
-        <v>22.406</v>
+        <v>22.147</v>
       </c>
       <c r="L43" t="n">
-        <v>12.219</v>
+        <v>12.088</v>
       </c>
       <c r="M43" t="n">
-        <v>7.594</v>
+        <v>7.618</v>
       </c>
       <c r="N43" t="n">
-        <v>5.469</v>
+        <v>5.441</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>13.688</v>
+        <v>13.588</v>
       </c>
       <c r="Q43" t="n">
-        <v>12.875</v>
+        <v>12.794</v>
       </c>
       <c r="R43" t="n">
-        <v>23.625</v>
+        <v>23.647</v>
       </c>
       <c r="S43" t="n">
-        <v>22.094</v>
+        <v>22.118</v>
       </c>
       <c r="T43" t="n">
-        <v>3288</v>
+        <v>3469</v>
       </c>
       <c r="U43" t="n">
-        <v>12.938</v>
+        <v>12.824</v>
       </c>
       <c r="V43" t="n">
-        <v>11.969</v>
+        <v>11.941</v>
       </c>
       <c r="W43" t="n">
-        <v>4.75</v>
+        <v>4.647</v>
       </c>
       <c r="X43" t="n">
-        <v>2.719</v>
+        <v>2.676</v>
       </c>
       <c r="Y43" t="n">
-        <v>29.812</v>
+        <v>29.353</v>
       </c>
       <c r="Z43" t="n">
-        <v>39.312</v>
+        <v>38.941</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.812</v>
+        <v>4.794</v>
       </c>
       <c r="AC43" t="n">
-        <v>11.031</v>
+        <v>11.029</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="AE43" t="n">
-        <v>3.5</v>
+        <v>3.471</v>
       </c>
       <c r="AF43" t="n">
-        <v>8.843999999999999</v>
+        <v>9.058999999999999</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.396</v>
+        <v>0.383</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.906</v>
+        <v>3.765</v>
       </c>
       <c r="AI43" t="n">
-        <v>8.688000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.45</v>
+        <v>0.443</v>
       </c>
       <c r="AK43" t="n">
-        <v>6.594</v>
+        <v>6.971</v>
       </c>
       <c r="AL43" t="n">
-        <v>19.844</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.332</v>
+        <v>0.349</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
@@ -7001,34 +7001,34 @@
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>89.611</v>
+        <v>89.34099999999999</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.6</v>
+        <v>0.601</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.017</v>
+        <v>1.019</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.249</v>
+        <v>0.247</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.331</v>
+        <v>1.327</v>
       </c>
       <c r="AV43" t="n">
         <v>0.2</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -7041,118 +7041,118 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C44" t="n">
-        <v>92.96899999999999</v>
+        <v>93.265</v>
       </c>
       <c r="D44" t="n">
-        <v>21.125</v>
+        <v>21.294</v>
       </c>
       <c r="E44" t="n">
-        <v>36.156</v>
+        <v>36.353</v>
       </c>
       <c r="F44" t="n">
-        <v>11.062</v>
+        <v>11.059</v>
       </c>
       <c r="G44" t="n">
-        <v>28.594</v>
+        <v>28.441</v>
       </c>
       <c r="H44" t="n">
-        <v>17.531</v>
+        <v>17.5</v>
       </c>
       <c r="I44" t="n">
-        <v>23.938</v>
+        <v>23.882</v>
       </c>
       <c r="J44" t="n">
-        <v>19.656</v>
+        <v>19.912</v>
       </c>
       <c r="K44" t="n">
-        <v>23.094</v>
+        <v>23.353</v>
       </c>
       <c r="L44" t="n">
-        <v>12.062</v>
+        <v>12.235</v>
       </c>
       <c r="M44" t="n">
-        <v>7.938</v>
+        <v>7.882</v>
       </c>
       <c r="N44" t="n">
-        <v>5.438</v>
+        <v>5.382</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>14.5</v>
+        <v>14.559</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.656</v>
+        <v>13.735</v>
       </c>
       <c r="R44" t="n">
-        <v>22.281</v>
+        <v>22.265</v>
       </c>
       <c r="S44" t="n">
-        <v>23.281</v>
+        <v>23.324</v>
       </c>
       <c r="T44" t="n">
-        <v>3478</v>
+        <v>3730</v>
       </c>
       <c r="U44" t="n">
-        <v>12.094</v>
+        <v>12.294</v>
       </c>
       <c r="V44" t="n">
-        <v>12.281</v>
+        <v>11.971</v>
       </c>
       <c r="W44" t="n">
-        <v>6.344</v>
+        <v>6.353</v>
       </c>
       <c r="X44" t="n">
-        <v>3.875</v>
+        <v>3.824</v>
       </c>
       <c r="Y44" t="n">
-        <v>32.375</v>
+        <v>32.441</v>
       </c>
       <c r="Z44" t="n">
-        <v>44.031</v>
+        <v>44.118</v>
       </c>
       <c r="AA44" t="n">
         <v>0.735</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.844</v>
+        <v>3.735</v>
       </c>
       <c r="AC44" t="n">
-        <v>9</v>
+        <v>8.824</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.427</v>
+        <v>0.423</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.438</v>
+        <v>2.618</v>
       </c>
       <c r="AF44" t="n">
-        <v>7.062</v>
+        <v>7.294</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.345</v>
+        <v>0.359</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.438</v>
+        <v>3.441</v>
       </c>
       <c r="AI44" t="n">
-        <v>8.5</v>
+        <v>8.471</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.404</v>
+        <v>0.406</v>
       </c>
       <c r="AK44" t="n">
-        <v>7.625</v>
+        <v>7.618</v>
       </c>
       <c r="AL44" t="n">
-        <v>20.094</v>
+        <v>19.971</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
@@ -7160,34 +7160,34 @@
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>89.782</v>
+        <v>89.861</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.583</v>
+        <v>0.585</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.617</v>
+        <v>0.619</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.035</v>
+        <v>1.038</v>
       </c>
       <c r="AS44" t="n">
         <v>0.162</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.356</v>
+        <v>1.368</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.2</v>
+        <v>0.201</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.068</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
